--- a/results/Int Task Remove ACC -0.2/Rando_fi_all.xlsx
+++ b/results/Int Task Remove ACC -0.2/Rando_fi_all.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.002420856610800759 +/- 0.0017213438390890116</t>
+          <t>0.0036623215394165575 +/- 0.0014344158917804317</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -886,157 +886,157 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.00710738671632527 +/- 0.00139802676965305</t>
+          <t>0.00648665425201741 +/- 0.0016507866104248418</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0006207324643079049 +/- 0.0010199675186316033</t>
+          <t>0.006517690875232807 +/- 0.0014154878027301367</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.0031967721911855818 +/- 0.0018046668851777216</t>
+          <t>0.0013345747982619783 +/- 0.0021098056361710028</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.0022967101179391714 +/- 0.0017731665868511068</t>
+          <t>0.006641837368094383 +/- 0.0015217443416674313</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0014276846679081468 +/- 0.0009834251718035358</t>
+          <t>0.004810676598386132 +/- 0.0016201592968514153</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0002482929857231753 +/- 0.00012414649286158762</t>
+          <t>0.00021725636250778945 +/- 0.0002424037764092665</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0011483550589695857 +/- 0.0011280435658216044</t>
+          <t>0.006114214773432691 +/- 0.0017449649654711936</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.001303538175046548 +/- 0.0015128563137124895</t>
+          <t>0.011638733705772852 +/- 0.002160336257640575</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.00313469894475481 +/- 0.0023573536128812193</t>
+          <t>0.0205152079453756 +/- 0.0028696710895627173</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.0007138423339540734 +/- 0.0017283247414433133</t>
+          <t>-0.0017070142768466523 +/- 0.0015093502688749664</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.0032588454376163978 +/- 0.0015346660850498013</t>
+          <t>0.0035381750465549922 +/- 0.0012116214336401808</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.006828057107386732 +/- 0.0015330960937589553</t>
+          <t>0.009248913718187502 +/- 0.0013656114214773353</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.0035692116697703335 +/- 0.00211982635835248</t>
+          <t>0.01154562383612665 +/- 0.0019071746115129932</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.0036933581626319213 +/- 0.001510626135771305</t>
+          <t>0.007293606455617674 +/- 0.0024050879908205395</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.0014276846679081357 +/- 0.0015406174607065033</t>
+          <t>0.0018311607697082954 +/- 0.0013273373544595293</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.0012104283054003907 +/- 0.0011399359200625128</t>
+          <t>0.0036623215394165575 +/- 0.0009696151056370773</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.0019863438857852466 +/- 0.0011711956712671075</t>
+          <t>0.002141527001862231 +/- 0.0008936176318366138</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.008007448789571691 +/- 0.0007448789571694759</t>
+          <t>0.004593420235878354 +/- 0.0012163822434677566</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>3.103662321539691e-05 +/- 0.00016713733107184917</t>
+          <t>0.00015518311607699565 +/- 0.0002081999979050019</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.014245810055865915 +/- 0.003623318068261885</t>
+          <t>-0.004407200496585928 +/- 0.003033978748566098</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.005307262569832405 +/- 0.0013200602307968177</t>
+          <t>0.004562383612662968 +/- 0.001186313771174187</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>-0.003662321539416502 +/- 0.0014004362722133388</t>
+          <t>0.001179391682185027 +/- 0.0010999407291539013</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.0013345747982619228 +/- 0.0010933528835386942</t>
+          <t>0.0012414649286157987 +/- 0.0011190413642036003</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.004438237119801347 +/- 0.0021549789369137043</t>
+          <t>-0.0012725015518311289 +/- 0.0018850756845512268</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.00018621973929234815 +/- 0.0004848075528185372</t>
+          <t>-0.001427684667908069 +/- 0.00048480755281854004</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>-0.0014897579143389073 +/- 0.002850642458896341</t>
+          <t>0.004158907510862853 +/- 0.0014570694716704545</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.0004345127250155234 +/- 0.0011293237367262876</t>
+          <t>0.008969584109248951 +/- 0.0015106261357713232</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.0027932960893854663 +/- 0.001225848395911327</t>
+          <t>0.002296710117939205 +/- 0.0019192582040646004</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0035381750465549476 +/- 0.0013182346729730047</t>
+          <t>0.007914338919925535 +/- 0.0014035281259584126</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-0.00024829298572314195 +/- 0.00045614334130040363</t>
+          <t>0.0008379888268156832 +/- 0.0006058107168200934</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.0003414028553693216 +/- 0.0008027633244182221</t>
+          <t>0.0007448789571695147 +/- 0.00028445535040074073</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1046,122 +1046,122 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.004934823091247676 +/- 0.0013200602307968227</t>
+          <t>0.003972687771570493 +/- 0.001658645464418043</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.0016449410304158695 +/- 0.0015207945375543001</t>
+          <t>0.0012104283054004017 +/- 0.001885075684551227</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>-0.0006828057107386542 +/- 0.00047679365287825167</t>
+          <t>-0.0009000620732463882 +/- 0.00029279891781677965</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-0.0014897579143389073 +/- 0.0006330253896452796</t>
+          <t>-0.0010242085661079647 +/- 0.000417555060430602</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.0037554314090626926 +/- 0.0012056439850747982</t>
+          <t>-0.002513966480446883 +/- 0.0017471716877762104</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>-0.0002793296089385278 +/- 0.00160942174580561</t>
+          <t>0.001427684667908169 +/- 0.0008578693334006972</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-0.0006517690875232684 +/- 0.0005276225946616991</t>
+          <t>-0.0012104283054003352 +/- 0.0006121378933369415</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.002017380509000599 +/- 0.0020173805090006095</t>
+          <t>0.0014897579143389517 +/- 0.0009495380844679278</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.008379888268156433 +/- 0.0014357583496238805</t>
+          <t>0.00710738671632527 +/- 0.0009357426090429092</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>-0.0004655493482308981 +/- 0.0012588019733502757</t>
+          <t>0.0026070763500931626 +/- 0.0009227851488093545</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.008752327746741163 +/- 0.0010460769426662206</t>
+          <t>0.005183116076970873 +/- 0.0013024292525361403</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>-0.00024829298572313083 +/- 0.0015874254317249348</t>
+          <t>0.0033829919304780077 +/- 0.001471869112523805</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0017690875232774794 +/- 0.001057524831620175</t>
+          <t>0.0031657355679702405 +/- 0.0012321187610974207</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-0.0035381750465549146 +/- 0.0019441911562217144</t>
+          <t>0.0009310986964618628 +/- 0.0018413900650765147</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-0.0007448789571694481 +/- 0.00042100124041745385</t>
+          <t>-0.0006207324643078382 +/- 0.00033998917287720784</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.002172563625077595 +/- 0.0010199675186315764</t>
+          <t>-0.004717566728739875 +/- 0.0014141261017870325</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.001148355058969619 +/- 0.0011021279270369132</t>
+          <t>0.011514587212911265 +/- 0.0017249774340894113</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.00031036623215395797 +/- 0.0013094365679533874</t>
+          <t>-0.0016449410304158474 +/- 0.0007979491081429219</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.0027622594661700917 +/- 0.0008494060945626341</t>
+          <t>0.0027001862197393424 +/- 0.0012950121691511468</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-0.00021725636250775616 +/- 0.0003119142030143033</t>
+          <t>3.3306690738754695e-17 +/- 0.0006656614087376456</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>-3.1036623215385804e-05 +/- 0.00029279891781678203</t>
+          <t>0.00046554934823096473 +/- 0.0007882324704655652</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>-0.0024518932340161226 +/- 0.0003525082772067315</t>
+          <t>-0.0016139044072004394 +/- 0.0002705710082892965</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.002172563625077595 +/- 0.0010570692964572423</t>
+          <t>-0.00521415270018617 +/- 0.0008756508987998626</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.002327746741154568 +/- 0.0020173805090006177</t>
+          <t>0.011452513966480471 +/- 0.0013200602307968123</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1171,92 +1171,92 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.0005586592178770999 +/- 0.0007827138555504957</t>
+          <t>0.002513966480446972 +/- 0.0006863235377869574</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-0.0027932960893854776 +/- 0.000519342040058382</t>
+          <t>-0.001458721291123466 +/- 0.0012725015518311646</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.004624456859093728 +/- 0.001267951472117653</t>
+          <t>0.011390440720049678 +/- 0.0018779080704414617</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.0002482929857231753 +/- 0.0011086636312533599</t>
+          <t>0.0006207324643079159 +/- 0.0004603475162691394</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-0.0035071384233395066 +/- 0.0007734286650761693</t>
+          <t>0.0012725015518312178 +/- 0.0009661317452683535</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.0025139664804469273 +/- 0.0013053842858356945</t>
+          <t>-0.007603972687771543 +/- 0.0020363904037646458</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>0.005338299193047813 +/- 0.0024232428672803365</t>
+          <t>-0.0019553072625697943 +/- 0.0009720955781108376</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0.0073246430788330265 +/- 0.0007238922277896102</t>
+          <t>0.008472998137802645 +/- 0.0016888600695732752</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>9.310986964619072e-05 +/- 0.00014222767520038004</t>
+          <t>-0.00037243947858465185 +/- 0.00012414649286158762</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>-0.003382991930477952 +/- 0.0018850756845512431</t>
+          <t>-0.0029484792054623953 +/- 0.0010773777130794555</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.0020173805090006325 +/- 0.0007111383760018349</t>
+          <t>0.0058659217877095274 +/- 0.001591364834673405</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.0015828677839851203 +/- 0.0007532378087840827</t>
+          <t>0.00043451272501556784 +/- 0.0003724394785847407</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.015456238361266306 +/- 0.0015752424010489722</t>
+          <t>0.0036002482929857636 +/- 0.001489757914338922</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.00021725636250777836 +/- 0.0009720955781108564</t>
+          <t>-0.0023898199875853066 +/- 0.0012183604237362216</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.00453134698944756 +/- 0.0017179829302418467</t>
+          <t>-0.003600248292985675 +/- 0.0019242706393544325</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>-9.310986964619072e-05 +/- 0.00014222767520038004</t>
+          <t>2.2204460492503132e-17 +/- 0.00019629284048219077</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>-0.002110490378646779 +/- 0.000601822452813948</t>
+          <t>-0.0012725015518311178 +/- 0.0004266830256010949</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>-0.0011793916821849714 +/- 0.0006771391753343024</t>
+          <t>0.0010242085661080536 +/- 0.0004400200769322661</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,52 +1266,52 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.0007448789571694814 +/- 0.0006539822317102751</t>
+          <t>0.0022967101179392157 +/- 0.0005921410312954441</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.01281812538795779 +/- 0.0018520830226984204</t>
+          <t>0.008690254500310413 +/- 0.0012946401995415214</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.310986964619072e-05 +/- 0.00019873135435857897</t>
+          <t>9.310986964619072e-05 +/- 0.00014222767520038007</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>-0.0007448789571694481 +/- 0.0005756436061760051</t>
+          <t>0.0004965859714463506 +/- 0.000523038471333114</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.00021725636250777836 +/- 0.0007084240974868407</t>
+          <t>0.00018621973929241475 +/- 0.0011629418991431113</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.0009000620732464548 +/- 0.0018593501925201791</t>
+          <t>0.009000620732464337 +/- 0.0013740498833754583</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.002203600248293003 +/- 0.0009760512224404853</t>
+          <t>0.0023587833643699875 +/- 0.0011956151635169575</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.0013656114214773529 +/- 0.001154629127109769</t>
+          <t>0.004314090626939815 +/- 0.0011814318007867326</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.0030415890751086415 +/- 0.001224275786673868</t>
+          <t>0.0025450031036623466 +/- 0.0011679011621493836</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.0006828057107386764 +/- 0.0006627609094991412</t>
+          <t>-0.0008690254500309913 +/- 0.001351430233213968</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.006831056314561812 +/- 0.0015288330219199566</t>
+          <t>0.01542819060313234 +/- 0.0016664444851783018</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1331,157 +1331,157 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.020426524491836073 +/- 0.0014905877538384047</t>
+          <t>-0.003965344885038291 +/- 0.0024732635140304465</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.006064645118293899 +/- 0.0021274094901049486</t>
+          <t>0.014328557147617483 +/- 0.00206490281703829</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.0020326557814062006 +/- 0.0011776472540534462</t>
+          <t>0.0029656781072976202 +/- 0.0023724395216697834</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.00016661112962347292 +/- 0.0020876314705334485</t>
+          <t>0.0033655448183939176 +/- 0.0017723540349180004</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.005431522825724744 +/- 0.0011451409715054906</t>
+          <t>-0.010396534488503806 +/- 0.002224367779843888</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.664445184938473e-05 +/- 0.0004420692822866323</t>
+          <t>0.0009330223258913861 +/- 0.0006108064904972903</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.010463178940353202 +/- 0.0011368691842207166</t>
+          <t>-0.008263912029323505 +/- 0.0017807916315744552</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.032022659113628796 +/- 0.0029028612695464226</t>
+          <t>0.0240919693435522 +/- 0.0030759501102017098</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.03332222592469177 +/- 0.002698894599309114</t>
+          <t>0.027090969676774445 +/- 0.0024759557465191284</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.0004998333888703854 +/- 0.0016810394209436402</t>
+          <t>-0.000333222259246857 +/- 0.0014293642512180538</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3.3322225924681256e-05 +/- 0.0019283753810370413</t>
+          <t>0.012995668110629832 +/- 0.0015911144800150887</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.0009663445518160674 +/- 0.0023864390896093067</t>
+          <t>0.025724758413862105 +/- 0.0027871407752517842</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-0.023792069310229935 +/- 0.003595713684829381</t>
+          <t>-0.021192935688103896 +/- 0.0027767632997000385</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-0.0006997667444185396 +/- 0.001478620975163891</t>
+          <t>0.001266244585138332 +/- 0.0029194529975087582</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>-0.006364545151616141 +/- 0.00192260869533512</t>
+          <t>-0.003798733755414807 +/- 0.0019893117702898273</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-0.00566477840719759 +/- 0.0012106565894425374</t>
+          <t>0.011162945684771797 +/- 0.0019156657583211916</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>-0.006464511829390196 +/- 0.0020497909362518912</t>
+          <t>0.006064645118293954 +/- 0.0018360516246525669</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>-0.004598467177607468 +/- 0.0013144340502043077</t>
+          <t>0.014928357214261934 +/- 0.0023458468386268663</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>6.664445184938473e-05 +/- 0.0004420692822866323</t>
+          <t>-0.00019993335554813196 +/- 0.000339821360452677</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.003965344885038302 +/- 0.0015009804237994205</t>
+          <t>0.009463512162612497 +/- 0.0022313454238964683</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-0.010429856714428531 +/- 0.0013662112629123403</t>
+          <t>-0.002299233588803662 +/- 0.0011295202436973405</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-0.0001666111296234618 +/- 0.0013349700515835046</t>
+          <t>0.0004998333888704076 +/- 0.001301274521144053</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>-0.0016327890703099035 +/- 0.0015302849054588468</t>
+          <t>-0.00023325558147277992 +/- 0.0013333054997495615</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00019993335554815416 +/- 0.0009565278303503885</t>
+          <t>0.004931689436854447 +/- 0.0011715025545649231</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.0006997667444185396 +/- 0.0005857512772824811</t>
+          <t>-0.0004331889370209452 +/- 0.0004228116474657881</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>-0.009863378873708773 +/- 0.0030620206618221044</t>
+          <t>0.0016661112962346291 +/- 0.0031009370540837976</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-0.008797067644118639 +/- 0.00139953348883704</t>
+          <t>-0.0026324558480506077 +/- 0.0020993002332555925</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>-0.007797400866377901 +/- 0.001383574774543623</t>
+          <t>-0.004698433855381512 +/- 0.002418789662640389</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.0051649450183272275 +/- 0.0023668165087743784</t>
+          <t>-0.0007664111962678688 +/- 0.0024261235120649613</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-0.002032655781406234 +/- 0.000822323404148836</t>
+          <t>2.2204460492503132e-17 +/- 0.0006829024169249724</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.0009996667777407708 +/- 0.000868937341579842</t>
+          <t>0.0011662779073642326 +/- 0.0008847662810631116</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1491,122 +1491,122 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.004498500499833391 +/- 0.0017711006019217937</t>
+          <t>-0.0007664111962678799 +/- 0.0023752460362808036</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.011929356881039655 +/- 0.0018420892983785854</t>
+          <t>0.010129956681106344 +/- 0.002241275804171984</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>-0.006064645118293899 +/- 0.0009634676637654926</t>
+          <t>-0.0009996667777407043 +/- 0.0009657698597926734</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-0.0003998667110963083 +/- 0.0004897347036554259</t>
+          <t>-0.001932689103632057 +/- 0.000986247823188849</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.005531489503498832 +/- 0.0019441455709183512</t>
+          <t>-0.001832722425857991 +/- 0.0015788547471485587</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>0.002265911362879036 +/- 0.0018779077379014102</t>
+          <t>0.0023325558147284653 +/- 0.0012378657528161973</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-0.001299566811062991 +/- 0.0012858234842768926</t>
+          <t>0.0020659780073309262 +/- 0.000771465305084334</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.0027324225258247405 +/- 0.0012360704425852078</t>
+          <t>0.01079640119960018 +/- 0.001926935327530949</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.0043318893702099185 +/- 0.00175060653602982</t>
+          <t>0.0022659113628790807 +/- 0.0010930502810301244</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>-0.004998333888703743 +/- 0.0014448172868163404</t>
+          <t>-0.0032989003665444437 +/- 0.0015802606732928264</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-0.012762412529156952 +/- 0.001437497808072201</t>
+          <t>-0.009896701099633398 +/- 0.0019603553588914114</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.004865044985004996 +/- 0.0013995334888370495</t>
+          <t>0.008163945351549518 +/- 0.0022365643711495914</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-0.0010663112295901445 +/- 0.0015827180389254214</t>
+          <t>0.005831389536821085 +/- 0.0019214532813513396</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.00156614461846053 +/- 0.0010329890036654442</t>
+          <t>-3.332222592465906e-05 +/- 0.0011963560860390548</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-6.664445184938473e-05 +/- 0.00029049643075913036</t>
+          <t>0.0008997000999666938 +/- 0.0009430837519550255</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>-0.0023658780406531467 +/- 0.0010479297030000832</t>
+          <t>0.003598800399866775 +/- 0.0010828441725606272</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>-0.0025658113962012674 +/- 0.0014062611026997005</t>
+          <t>0.008463845384871771 +/- 0.002784749405634958</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-0.006664445184938339 +/- 0.0023843443945349373</t>
+          <t>-0.011262912362545775 +/- 0.002079904902942658</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-0.0025991336221259597 +/- 0.0020037715932519676</t>
+          <t>-0.005964678440519777 +/- 0.0021463755968261044</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-0.00013328890369876945 +/- 0.0005809928615182607</t>
+          <t>0.0009663445518161007 +/- 0.0011963560860390578</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>-0.0005331556147950778 +/- 0.000733088970343232</t>
+          <t>3.332222592471457e-05 +/- 0.0008357171745407618</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>-0.00239920026657785 +/- 0.00035889135669007663</t>
+          <t>-0.0003332222592468792 +/- 0.00039427389424185385</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-0.007430856381206286 +/- 0.0010329890036654631</t>
+          <t>-0.010963012329223542 +/- 0.002136004066716084</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.0020326557814062006 +/- 0.0017150428833665706</t>
+          <t>0.005664778407197635 +/- 0.002210346411433113</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1616,92 +1616,92 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-0.0013995334888370792 +/- 0.0006461419336776295</t>
+          <t>-0.00029990003332218683 +/- 0.0009119581595070682</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-0.005598133955348206 +/- 0.0008270358977668162</t>
+          <t>0.000333222259246968 +/- 0.0009884969659574047</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-0.0012329223592136064 +/- 0.001445201495648215</t>
+          <t>-0.003232255914695048 +/- 0.001406261102699738</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>-0.0022659113628790695 +/- 0.0005331556147950486</t>
+          <t>0.0020659780073309262 +/- 0.0007270051392626397</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-0.001966011329556816 +/- 0.0015590386624844365</t>
+          <t>0.004665111629456886 +/- 0.0017632464585568622</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0.0037320893035654667 +/- 0.0013560139919610507</t>
+          <t>-0.014428523825391493 +/- 0.0021024713834518257</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-0.0014328557147617494 +/- 0.0018852842598887976</t>
+          <t>0.006831056314561823 +/- 0.0007920602681776024</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>0.0010996334555148368 +/- 0.0016053568104559726</t>
+          <t>0.0026324558480506966 +/- 0.0014094159268615112</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>-0.0005331556147950778 +/- 0.0005205098084576337</t>
+          <t>0.0001666111296234618 +/- 0.0001666111296234618</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>-0.003998667110963005 +/- 0.0020756296571006207</t>
+          <t>-0.008563812062645726 +/- 0.0014528643356608876</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>-0.004365211596134589 +/- 0.0007664111962679243</t>
+          <t>-0.007330889703432153 +/- 0.0011250878384627685</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-0.003865378207264236 +/- 0.0008966094000048921</t>
+          <t>0.003032322559147005 +/- 0.0010584725207776655</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-0.00536487837387537 +/- 0.0017471145256805621</t>
+          <t>-0.005764745084971634 +/- 0.00236587804065312</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>-0.005531489503498843 +/- 0.0021398992813065456</t>
+          <t>0.0025658113962013116 +/- 0.001452864335660915</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>-0.005131622792402546 +/- 0.0019668583223423695</t>
+          <t>-0.0016661112962345404 +/- 0.0015486771127786916</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>0.00013328890369876945 +/- 0.0005205098084576337</t>
+          <t>-0.0004665111629456375 +/- 0.0004520046639869811</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>-0.0012662445851383097 +/- 0.000771465305084334</t>
+          <t>0.00029990003332223123 +/- 0.0005664778407197702</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>-0.0011329556814395404 +/- 0.0006697684519240965</t>
+          <t>0.0002665778073975389 +/- 0.0004420692822866323</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1711,52 +1711,52 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>-0.00019993335554815416 +/- 0.0007772011855841925</t>
+          <t>-0.0017994001999332766 +/- 0.0008586536972159517</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>-0.004365211596134622 +/- 0.0015375237580885358</t>
+          <t>0.0012995668110630022 +/- 0.0012596506612086728</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>3.332222592469236e-05 +/- 9.996667777407708e-05</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>-0.002232589136954388 +/- 0.0004724240879292928</t>
+          <t>0.0015328223925358485 +/- 0.0005205098084576337</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>-0.010163278907030981 +/- 0.0015718062532583323</t>
+          <t>-0.0008997000999666383 +/- 0.0015346323145177376</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>-0.005998000666444503 +/- 0.0017378746831596607</t>
+          <t>-0.0038320559813395105 +/- 0.0008972283917251916</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>-3.332222592469236e-05 +/- 0.00048173383188274637</t>
+          <t>0.000833055648117309 +/- 0.0006189328764080986</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>-0.0048983672109296885 +/- 0.001788568730465795</t>
+          <t>0.00046651116294571526 +/- 0.0011846976897454807</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>-9.996667777408818e-05 +/- 0.00141413496660599</t>
+          <t>-0.003865378207264203 +/- 0.0016405909530278428</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>-0.0035988003998667084 +/- 0.0012179718015659245</t>
+          <t>0.002299233588803773 +/- 0.0009594255280831872</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.00044987146529568145 +/- 0.0009111469716425293</t>
+          <t>-0.005302056555269896 +/- 0.0012044771731356831</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1776,157 +1776,157 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.0057519280205655995 +/- 0.001020718520197224</t>
+          <t>-0.005687660668380445 +/- 0.0019121562399501044</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.004562982005141436 +/- 0.0016991393401545405</t>
+          <t>-0.004980719794344446 +/- 0.0015360434964931955</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.0018316195372751088 +/- 0.0012113159913220099</t>
+          <t>-0.002185089974293053 +/- 0.0009066025693872579</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.0031812339331619087 +/- 0.001564022303809486</t>
+          <t>-0.0021529562982004922 +/- 0.0009207293561629043</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.000706940874035944 +/- 0.0012428714399623096</t>
+          <t>0.0007390745501285711 +/- 0.0021414147919725044</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.00038560411311048257 +/- 0.00012853470437019788</t>
+          <t>-0.00012853470437015346 +/- 0.00015742221997317954</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.005012853470437051 +/- 0.0012210796915167162</t>
+          <t>-0.0028598971722364917 +/- 0.001117309681922469</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.01394601542416457 +/- 0.0018075014280752209</t>
+          <t>0.023907455012853508 +/- 0.003042365135872649</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.03329048843187665 +/- 0.003230033900547307</t>
+          <t>0.030430591259640104 +/- 0.0025948813924450394</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.0004177377892031431 +/- 0.0017836361293545008</t>
+          <t>-0.008001285347043663 +/- 0.001336158283180694</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-0.004434447300771171 +/- 0.001291757791917845</t>
+          <t>-0.007937017994858598 +/- 0.0008747209247311167</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.00025706940874039577 +/- 0.0014138817480719747</t>
+          <t>-0.006330334190231357 +/- 0.0019966884810933318</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.01995501285347049 +/- 0.0016909154391931739</t>
+          <t>0.01985861182519284 +/- 0.002140208972409608</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.02882390745501291 +/- 0.0024177254892000714</t>
+          <t>0.02214010282776352 +/- 0.0023369380251384063</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.0012210796915167466 +/- 0.0014138817480719688</t>
+          <t>-0.0008033419023135924 +/- 0.0015494297495168752</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>4.4408920985006264e-17 +/- 0.0008622370093186645</t>
+          <t>-0.0032776349614395796 +/- 0.0014284132886177965</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.0017994858611825593 +/- 0.0011242195170010055</t>
+          <t>-0.002345758354755767 +/- 0.001236624768952062</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-0.0015745501285346687 +/- 0.0009581009971642272</t>
+          <t>-0.004755784061696644 +/- 0.00040134948575823486</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.0001928020565552968 +/- 0.0003277004828787158</t>
+          <t>-0.0006105398457583288 +/- 0.00017304514161745678</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.006844473007712138 +/- 0.002037639956617963</t>
+          <t>-0.001060411311053977 +/- 0.002067821406580497</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.002506426735218459 +/- 0.001226142932412534</t>
+          <t>-0.0032455012853470078 +/- 0.0008794300889077152</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.00504498714652959 +/- 0.00120276139281574</t>
+          <t>-0.0006426735218508561 +/- 0.0007871110998660653</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.0015102827763496362 +/- 0.000593386417500621</t>
+          <t>-0.001381748071979405 +/- 0.0013862245893395474</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00025706940874039577 +/- 0.0009618656521269742</t>
+          <t>-0.0014138817480719656 +/- 0.0017435295586440123</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-9.640102827759289e-05 +/- 0.0003229394479794584</t>
+          <t>-0.0006748071979434278 +/- 0.00044176500915386186</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.0015102827763496696 +/- 0.0017951770852780685</t>
+          <t>-0.002731362467866316 +/- 0.0020437119043904823</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-0.009543701799485816 +/- 0.0013936534988561126</t>
+          <t>-0.013206940874035965 +/- 0.0015574062745568977</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.0009640102827763952 +/- 0.001378381143285822</t>
+          <t>-0.0053984575835475555 +/- 0.0013618007776617744</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.003727506426735172 +/- 0.001364830371567812</t>
+          <t>-0.010347043701799463 +/- 0.0015330154809609822</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>-0.0014781491002570201 +/- 0.00038560411311054546</t>
+          <t>-0.00016066838046269183 +/- 0.00032927219684959866</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.001606683804627207 +/- 0.0006740416762019062</t>
+          <t>6.426735218511004e-05 +/- 0.0004013494857582527</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1936,122 +1936,122 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.0020244215938303722 +/- 0.0009428920791209054</t>
+          <t>-0.011632390745501242 +/- 0.001471146933452375</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.007840616966580938 +/- 0.0012378766249523385</t>
+          <t>-0.012853470437017966 +/- 0.0015276175223656425</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.00022493573264785737 +/- 0.0005386585672956407</t>
+          <t>-0.0008997429305912519 +/- 0.00024046641303174224</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.0006426735218509561 +/- 0.0003520067850290356</t>
+          <t>-0.00025706940874034025 +/- 0.0006062969879213719</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.00044987146529568145 +/- 0.0014167999797588997</t>
+          <t>0.003438303341902338 +/- 0.0017187762365445014</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>-0.0014781491002570312 +/- 0.0016334530883211859</t>
+          <t>-0.011503856041131067 +/- 0.0020312957107042513</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-0.00035347043701794423 +/- 0.0005462724935732554</t>
+          <t>-0.0016388174807197785 +/- 0.000680900388830885</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.0013174807197943838 +/- 0.0011802292848462229</t>
+          <t>0.0007069408740360105 +/- 0.001985018664714693</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.0009961439588688447 +/- 0.001272834339353379</t>
+          <t>-0.006715938303341884 +/- 0.0016159757018868975</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-0.003823907455012809 +/- 0.0011265133767967977</t>
+          <t>0.0005141388174807138 +/- 0.001262653130102093</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.0011568123393316699 +/- 0.001096318901621599</t>
+          <t>-0.0070372750642673345 +/- 0.0016287051282100403</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>-0.0005141388174806805 +/- 0.0019344366251018603</t>
+          <t>0.004627249357326513 +/- 0.0014669295900402689</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.00044987146529567034 +/- 0.001278904160805415</t>
+          <t>-0.0006105398457583288 +/- 0.0012147209621745305</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.0012210796915167466 +/- 0.0010830526700740804</t>
+          <t>0.0022814910025707237 +/- 0.0014686882881782004</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.0005462724935733076 +/- 0.00038156626243695846</t>
+          <t>0.0003213367609254614 +/- 0.000248906384717692</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>6.426735218514334e-05 +/- 0.0010734764195687644</t>
+          <t>-0.00019280205655524129 +/- 0.000864628794799062</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>-0.0032455012853469857 +/- 0.000792992460106239</t>
+          <t>0.004755784061696677 +/- 0.0013388603249357147</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-0.0008997429305912186 +/- 0.001512673816958835</t>
+          <t>-0.004338046272493556 +/- 0.0017079283118146848</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-0.002088688946015371 +/- 0.001652620934527493</t>
+          <t>-0.005816195372750621 +/- 0.0010105517476552963</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.0009318766066838457 +/- 0.00044176500915383914</t>
+          <t>-9.640102827759289e-05 +/- 0.0003815662624369528</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>-0.0006105398457583288 +/- 0.000507060855978762</t>
+          <t>-0.00035347043701796645 +/- 0.00026692236063360734</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>3.213367609254947e-05 +/- 9.64010282776484e-05</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-0.004948586118251874 +/- 0.001976678213268609</t>
+          <t>-0.009897172236503837 +/- 0.0018335915961037164</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-0.00411311053984571 +/- 0.0014356239012653226</t>
+          <t>0.00048200514138820873 +/- 0.0015427511419226212</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2061,92 +2061,92 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-0.0007712082262210429 +/- 0.0006130714662062801</t>
+          <t>-0.0012853470437017788 +/- 0.0008001220821329387</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.003920308483290558 +/- 0.0010342851503490288</t>
+          <t>-0.0020886889460154045 +/- 0.0007772099371753037</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-0.00584832904884317 +/- 0.0013541971404694869</t>
+          <t>-0.0011568123393316254 +/- 0.0014094930719448246</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.00012853470437020897 +/- 0.0006616728882382429</t>
+          <t>-0.0011889460154241305 +/- 0.0007192490130334184</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.0017994858611825593 +/- 0.0009661501528517326</t>
+          <t>-6.426735218505453e-05 +/- 0.0007712082262210892</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-0.004402313624678611 +/- 0.0015876117386935376</t>
+          <t>0.000578406169665846 +/- 0.0013311256540622161</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-0.0020886889460153824 +/- 0.0005611905268821481</t>
+          <t>-0.0013496143958868668 +/- 0.0015530907421072533</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.002313624678663262 +/- 0.0012091830155672783</t>
+          <t>0.002249357326478174 +/- 0.0009088776107796213</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.00012853470437020897 +/- 0.0002570694087403763</t>
+          <t>-9.64010282776151e-05 +/- 0.00014725500305124987</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.004659383033419085 +/- 0.000561190526882164</t>
+          <t>0.000353470437018033 +/- 0.0013591443433519884</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.0018958868894601965 +/- 0.0005462724935732756</t>
+          <t>-0.0017994858611825148 +/- 0.0019450830270464684</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-0.0002892030848328786 +/- 0.00048627075676161547</t>
+          <t>-0.0008033419023135924 +/- 0.00038694069983266974</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.013496143958868934 +/- 0.0011585961682082212</t>
+          <t>0.010796915167095144 +/- 0.0018692852920628564</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>-0.0006105398457583067 +/- 0.0008059084964000387</t>
+          <t>-0.006426735218508983 +/- 0.0011937130861829346</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.0020565552699229215 +/- 0.0017316444197053478</t>
+          <t>0.005816195372750665 +/- 0.001162599776036358</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.0004177377892031431 +/- 0.00014725500305130075</t>
+          <t>-6.426735218507673e-05 +/- 0.00012853470437015346</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>-0.00022493573264777966 +/- 0.0004323143973995368</t>
+          <t>-0.0009640102827763397 +/- 0.0003520067850290356</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>-0.0010604113110539548 +/- 0.0004777014378958368</t>
+          <t>-0.0002892030848328675 +/- 0.00022493573264780346</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.00038560411311058254 +/- 0.0005712207209071775</t>
+          <t>0.0005462724935732632 +/- 0.00025097203328747984</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>-0.0003213367609254059 +/- 0.001185031421245863</t>
+          <t>-0.001606683804627218 +/- 0.0007040135700580561</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2171,37 +2171,37 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.0003856041131105936 +/- 0.0001928020565552968</t>
+          <t>-0.00022493573264777966 +/- 0.0003534704370179957</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.640102827769281e-05 +/- 0.000874720924731121</t>
+          <t>-0.002377892030848305 +/- 0.0008764898262844251</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>-0.0005462724935732189 +/- 0.0008628355772556136</t>
+          <t>-0.0039524421593830185 +/- 0.0013561020466586915</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.00048200514138820873 +/- 0.00043706524771002387</t>
+          <t>-0.001735218508997416 +/- 0.0004809328260634904</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>-0.0018316195372750088 +/- 0.0010166640115396267</t>
+          <t>-0.0015424164524421413 +/- 0.0009401503109465138</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.0057197943444730615 +/- 0.001014121711957554</t>
+          <t>0.000803341902313659 +/- 0.00106817288808449</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>-0.0004498714652956037 +/- 0.0013572437070657382</t>
+          <t>-0.0009961439588688891 +/- 0.0008434707421855287</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.003921568627450955 +/- 0.0016251012098700839</t>
+          <t>0.007232401157184232 +/- 0.0011341869986742157</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2221,157 +2221,157 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.01076824172291867 +/- 0.0011158183836522105</t>
+          <t>0.002925104468016748 +/- 0.001629228659270235</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.001767920282867219 +/- 0.0017737550191348674</t>
+          <t>0.0027965284474446017 +/- 0.0013565379521703028</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.0026679524268723998 +/- 0.0017491183362793718</t>
+          <t>0.0035358405657345384 +/- 0.0009091697604455953</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.00636451301832206 +/- 0.0019699843710761383</t>
+          <t>0.007489553198328569 +/- 0.003284513390556496</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.002989392478302788 +/- 0.0018014987167087166</t>
+          <t>0.0066216650594664635 +/- 0.001819475628169059</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.000192864030858253 +/- 0.00015747282177970302</t>
+          <t>-3.214400514299776e-05 +/- 0.0003032459380281479</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0005785920925747035 +/- 0.0015994670915621615</t>
+          <t>0.004918032786885296 +/- 0.0012117053567965816</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-0.012343297974927692 +/- 0.004293842360526282</t>
+          <t>0.0015107682417229485 +/- 0.002875226907594133</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.026197364191578275 +/- 0.003628857453011047</t>
+          <t>-0.003021536483445786 +/- 0.0016590791257555897</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-0.0031501125040180322 +/- 0.001120899760473326</t>
+          <t>-0.001189328190292449 +/- 0.0008983084932486073</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.0027000964320154086 +/- 0.0014025987932672131</t>
+          <t>0.0026036644165863486 +/- 0.0014335649708117901</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.0026679524268723555 +/- 0.002375396308176462</t>
+          <t>0.007264545162327263 +/- 0.0021668016131600877</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-0.006782385085181641 +/- 0.0023154842125942786</t>
+          <t>0.0020572163291546542 +/- 0.0019773135968151174</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-0.005914496946319537 +/- 0.0027130759043406173</t>
+          <t>-0.00671809707489549 +/- 0.002597307222502825</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.004050144648023113 +/- 0.0016590791257555628</t>
+          <t>0.003471552555448454 +/- 0.0011208997604733296</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.005014464802314367 +/- 0.0011958261162158942</t>
+          <t>0.007810993249758968 +/- 0.0012286412634918992</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-0.0052394728383156845 +/- 0.0009431951623993045</t>
+          <t>-0.006943105110896774 +/- 0.0011245808861803852</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.214400514300886e-05 +/- 0.0016355582427783428</t>
+          <t>0.003439408550305423 +/- 0.001294170500752</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-0.00012857602057216865 +/- 0.00021321920863745023</t>
+          <t>3.214400514304216e-05 +/- 9.64320154291265e-05</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0030536804885888504 +/- 0.0014887221056778363</t>
+          <t>0.01928640308582452 +/- 0.0022865212785315</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.006589521054323366 +/- 0.0020644861103608397</t>
+          <t>-0.0048537447765991445 +/- 0.00048642706365870103</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.005785920925747345 +/- 0.0012937712502409573</t>
+          <t>0.006428801028608211 +/- 0.0010853065262702811</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.0014786242365798729 +/- 0.001058314216210499</t>
+          <t>-0.00022500803600123965 +/- 0.0011232018778306757</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.004403728704596599 +/- 0.0017667510232929897</t>
+          <t>0.0025715204114433064 +/- 0.0008861490679582198</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>9.64320154291154e-05 +/- 0.0008388292093024787</t>
+          <t>0.0013179042108647288 +/- 0.0005650400460060328</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>-0.009868209578913545 +/- 0.00177840902521673</t>
+          <t>0.006460945033751242 +/- 0.001648144486440941</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.003985856637737051 +/- 0.002474044539362766</t>
+          <t>-0.0016393442622950171 +/- 0.002458333501124886</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-0.012054001928640335 +/- 0.0010489983202880578</t>
+          <t>-0.0029572484731597015 +/- 0.0009068939877638056</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.009578913532626198 +/- 0.0007158809852561775</t>
+          <t>-0.007778849244615827 +/- 0.0020166360837490216</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0006428801028607878 +/- 0.0006428801028608044</t>
+          <t>0.0006750241080038854 +/- 0.00036508571814853816</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.00028929604628734616 +/- 0.0007531581172523119</t>
+          <t>0.0006750241080038854 +/- 0.00044190701012112156</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -2381,122 +2381,122 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.004339440694310503 +/- 0.0017024188591276482</t>
+          <t>-0.001607200257151975 +/- 0.0015549195271549788</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.002121504339440672 +/- 0.0018588019665446553</t>
+          <t>0.001157184185149518 +/- 0.0027016266653102743</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.00012857602057214645 +/- 0.0005222782645217453</t>
+          <t>0.0012214721954355912 +/- 0.0006711865322346923</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-0.0009643201542912427 +/- 0.0009426472708849413</t>
+          <t>3.214400514307547e-05 +/- 0.0004864270636586694</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.006428801028608178 +/- 0.0022910356388563765</t>
+          <t>0.0005785920925747923 +/- 0.0012180839165217968</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>-0.008453873352619745 +/- 0.001737263788733098</t>
+          <t>-0.007328833172613269 +/- 0.0009294009832723095</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-0.0030215364834458524 +/- 0.001038604591539929</t>
+          <t>0.002025072324011634 +/- 0.00040786170171806894</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.003182256509161063 +/- 0.0011979842593110915</t>
+          <t>0.0006107360977178122 +/- 0.0007932473596434097</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.007682417229186778 +/- 0.0012486611764419722</t>
+          <t>-0.007328833172613269 +/- 0.0013315535311609129</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-0.00012857602057217977 +/- 0.0016276424173799111</t>
+          <t>-0.001542912246865924 +/- 0.0011923649624552251</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-0.0035036965605914627 +/- 0.0018095105040228118</t>
+          <t>-0.006589521054323333 +/- 0.001432122752166212</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.00032144005143038836 +/- 0.0012197792324660894</t>
+          <t>0.0024108003857280847 +/- 0.0014103125019916565</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.0035036965605914406 +/- 0.0011806086578082318</t>
+          <t>0.0028608164577306862 +/- 0.0014761764710003206</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-0.004596592735454863 +/- 0.001880080850644785</t>
+          <t>-0.002185792349726734 +/- 0.0013996490554212266</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.00032144005143041053 +/- 0.0005750094445515424</t>
+          <t>0.00041787206685957036 +/- 0.0005388317137332035</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.0004500160720025681 +/- 0.0015090574856066253</t>
+          <t>-0.0003535840565733861 +/- 0.0005464480874316757</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>-0.006718097074895546 +/- 0.002504139724019572</t>
+          <t>0.0005143040822887191 +/- 0.0016714882674381233</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-0.012696882031501133 +/- 0.0010489983202880613</t>
+          <t>-0.006910961105753732 +/- 0.0008655038262832646</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-0.008293153326904557 +/- 0.0013159427509134515</t>
+          <t>-0.006300225008035976 +/- 0.0012793152518246332</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-0.00032144005143042165 +/- 0.0006098896162330784</t>
+          <t>0.0006107360977178122 +/- 0.0004178720668595234</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>-3.214400514304216e-05 +/- 0.0005650400460060327</t>
+          <t>0.001575056252009055 +/- 0.0006657767655804615</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.0006107360977177789 +/- 0.00022500803600126028</t>
+          <t>0.00016072002571521082 +/- 0.00021562854170683538</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-0.005625200900032168 +/- 0.0016088066546116543</t>
+          <t>6.428801028612874e-05 +/- 0.0018057951662087013</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.0028286724525875885 +/- 0.001889673861356362</t>
+          <t>0.004596592735454897 +/- 0.0017842094614436586</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2506,92 +2506,92 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-0.00012857602057217977 +/- 0.0005021054115015496</t>
+          <t>0.0013179042108647288 +/- 0.0003032459380281902</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-0.0018964963034394321 +/- 0.0017336916181500096</t>
+          <t>0.003921568627451011 +/- 0.0014855956294813667</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-0.013339762134361954 +/- 0.0018701624182306516</t>
+          <t>0.0021215043394407383 +/- 0.0017617730126704956</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>-0.0005464480874317168 +/- 0.00047785499027062445</t>
+          <t>0.0021536483445837697 +/- 0.0006750241080038406</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-0.0007071681131469055 +/- 0.0015535899676752734</t>
+          <t>0.0023465123754420115 +/- 0.001594614819005135</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-0.000192864030858253 +/- 0.001779280296123192</t>
+          <t>-0.0036965605914496603 +/- 0.0013350408008547113</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.0059466409514625455 +/- 0.0020893603342976475</t>
+          <t>-0.0007071681131468388 +/- 0.0011836678006764273</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.004757312761170018 +/- 0.0014855956294813704</t>
+          <t>0.005496624879460022 +/- 0.0012569086979117286</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.0004500160720025792 +/- 0.0002946046734140617</t>
+          <t>-0.0004500160720025015 +/- 0.00032780581893876714</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.007875281260044975 +/- 0.0018975856178907677</t>
+          <t>0.003278688524590201 +/- 0.0011300800920120112</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.0019607843137254832 +/- 0.001031116356949245</t>
+          <t>0.007521697203471622 +/- 0.0012044354866728036</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.002764384442301493 +/- 0.0012382745280783089</t>
+          <t>0.00012857602057221308 +/- 0.0010966713024256893</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-0.009996785599485724 +/- 0.0015243851753621773</t>
+          <t>0.004339440694310559 +/- 0.0010088302684972883</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.0010286081645772937 +/- 0.0015994670915621594</t>
+          <t>0.002410800385728107 +/- 0.0016779663305867196</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.0007393121182899254 +/- 0.002048408095963321</t>
+          <t>-0.0014464802314367864 +/- 0.001621600547171889</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.00012857602057215757 +/- 0.0005417004032900318</t>
+          <t>0.00012857602057217977 +/- 0.0002571520411443179</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>-0.001189328190292538 +/- 0.0006274259497249367</t>
+          <t>0.0009964641594343072 +/- 0.0003355932661173573</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>-0.004050144648023157 +/- 0.0010872089055151222</t>
+          <t>0.000771456123433023 +/- 0.000692403061026622</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2601,52 +2601,52 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>-0.0018322082931533478 +/- 0.0009755056834132679</t>
+          <t>-0.00324654451944707 +/- 0.0006811192574868784</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.0059144969463194915 +/- 0.0013423730644693804</t>
+          <t>0.0063966570234651795 +/- 0.00099022319516231</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>-0.0009000321440051807 +/- 0.0004014784955576123</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>9.64320154291154e-05 +/- 0.0008010244805128363</t>
+          <t>0.0008036001285760541 +/- 0.0002591532545258401</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>-0.0019607843137255166 +/- 0.001162973482168152</t>
+          <t>3.2144005143097675e-05 +/- 0.0010311163569492372</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>-0.0008036001285760319 +/- 0.0010291102920978418</t>
+          <t>0.006171648987463885 +/- 0.0010346176110209884</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.0008357441337190297 +/- 0.0009557099805412025</t>
+          <t>-0.0006428801028607656 +/- 0.001423075771210451</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>-0.0009643201542912539 +/- 0.001694815342521881</t>
+          <t>0.0008357441337190852 +/- 0.0010083180418745054</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>-0.0013821922211507687 +/- 0.0016890137776174278</t>
+          <t>0.002667952426872433 +/- 0.0011504680275263906</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.0018322082931533147 +/- 0.0011771027594728917</t>
+          <t>-0.0014786242365798508 +/- 0.0011153552923752613</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.0017823042647995059 +/- 0.0008911521323997291</t>
+          <t>0.0023870146403564994 +/- 0.0016306414331571698</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2666,157 +2666,157 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.0018777848504137773 +/- 0.000859325270528327</t>
+          <t>0.004105665181413165 +/- 0.0011514992052912396</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.0018777848504137663 +/- 0.0011861645546520714</t>
+          <t>0.0016549968173138585 +/- 0.0017303981182773208</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.0017186505410566656 +/- 0.0012010160575501643</t>
+          <t>-0.002959898154041962 +/- 0.0012081637744177404</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-6.365372374284028e-05 +/- 0.0012392057500911643</t>
+          <t>0.0015913430935710182 +/- 0.0014018278514032732</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.0012094207511139433 +/- 0.0013785110011271565</t>
+          <t>-0.0008911521323996974 +/- 0.0011633142509545973</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.000222788033099941 +/- 0.0003198560032183673</t>
+          <t>-3.182686187142014e-05 +/- 0.000222788033099941</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0001591343093571007 +/- 0.0007009139257016455</t>
+          <t>0.0010502864417568868 +/- 0.0013431539049019194</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.015563335455124139 +/- 0.0029564739301352998</t>
+          <t>0.005315085932527097 +/- 0.001402189100694493</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.00913430935709737 +/- 0.0033803963095746905</t>
+          <t>0.005824315722469819 +/- 0.0018451346964526727</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.0032463399108847656 +/- 0.0007504663349809863</t>
+          <t>0.005824315722469808 +/- 0.0009446735887750159</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.0015276893698281558 +/- 0.0011976376653231597</t>
+          <t>0.003341820496499115 +/- 0.0010579739107953539</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.0010502864417568647 +/- 0.0014657643462342067</t>
+          <t>0.0018777848504137995 +/- 0.0013611333405692692</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.03434118395926161 +/- 0.002606890054707228</t>
+          <t>0.0231063017186506 +/- 0.00317056891289938</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.0068109484404837665 +/- 0.0018238763567020165</t>
+          <t>0.004996817313812907 +/- 0.00255429156298324</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.0009866327180140023 +/- 0.0016868236791852385</t>
+          <t>0.0002227880330999743 +/- 0.001320335360451382</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.006556333545512438 +/- 0.0005728835136855626</t>
+          <t>0.0067154678548695616 +/- 0.0018418378480242305</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0.005760661998726935 +/- 0.0008593252705283438</t>
+          <t>0.002196053469128001 +/- 0.0016565262482079218</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.0057606619987269235 +/- 0.0010209430256107829</t>
+          <t>0.004264799490770288 +/- 0.0010951400721887412</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.0001591343093571007 +/- 0.0002135010799649748</t>
+          <t>0.0002864417568427813 +/- 0.00017139289647150275</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.009611712285168671 +/- 0.0025572640899555296</t>
+          <t>-0.002450668364099251 +/- 0.0013876657769950214</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.006110757479312556 +/- 0.001154573974997927</t>
+          <t>-0.005728835136855459 +/- 0.0010064537428925177</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.0012730744748568057 +/- 0.0006826101397048906</t>
+          <t>0.001113940165499716 +/- 0.0010579739107953354</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.0018777848504137329 +/- 0.0010974500095204452</t>
+          <t>-0.0023551877784849795 +/- 0.0008201208610264415</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.0028962444302991774 +/- 0.0010009029403893147</t>
+          <t>0.00219605346912799 +/- 0.0009595680096551019</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>6.365372374284028e-05 +/- 0.000528747540605872</t>
+          <t>-0.0007638446849139946 +/- 0.0004971514752327359</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>-0.0008593252705283328 +/- 0.001936214026003186</t>
+          <t>-0.00012730744748562506 +/- 0.0014736902486047218</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-0.004869509866327182 +/- 0.0017893943726124358</t>
+          <t>-0.009548058561425788 +/- 0.0012730744748567612</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-0.0031826861871419474 +/- 0.001288889670994037</t>
+          <t>-0.006460852959898111 +/- 0.0010464215291389647</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-0.00754296626352643 +/- 0.0012165190867992463</t>
+          <t>-0.010311903246339871 +/- 0.0010670308475009514</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0003182686187142014 +/- 0.0002846681066199664</t>
+          <t>-0.0004137492043283952 +/- 0.00045122364349957334</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.0003819223424570417 +/- 0.00019096117122852085</t>
+          <t>-0.00044557606619981537 +/- 0.00025461489497131116</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2826,122 +2826,122 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.003946530872055987 +/- 0.0007950347547292843</t>
+          <t>-0.01078930617441115 +/- 0.0019487294099098122</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.003787396562698908 +/- 0.0011514992052912474</t>
+          <t>-0.0025461489497135004 +/- 0.001129741524462076</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0.00025461489497136114 +/- 0.00042223103632787643</t>
+          <t>0.00031826861871422365 +/- 0.000725764115276331</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.0009229789942711841 +/- 0.0007724163653413016</t>
+          <t>-0.0010184595798853557 +/- 0.0005287475406058425</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.0016549968173138363 +/- 0.0008396502837856659</t>
+          <t>-0.0011139401654996384 +/- 0.000808302043233601</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>-0.0048058561425843305 +/- 0.0010109726399916564</t>
+          <t>-0.008943348185868828 +/- 0.001594204937793541</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>0.0005410566518141424 +/- 0.0002864417568427813</t>
+          <t>3.3306690738754695e-17 +/- 0.0006038722457355051</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.0012412476129853745 +/- 0.000759189079686597</t>
+          <t>0.0022915340547422502 +/- 0.001640241722052842</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.006842775302355208 +/- 0.0012264703289622985</t>
+          <t>-0.009643539147040059 +/- 0.001380346813634724</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>-0.0010184595798854335 +/- 0.0009737147384327398</t>
+          <t>-0.0021005728835136405 +/- 0.0012586709060015925</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.0010821133036282738 +/- 0.0010381608166963768</t>
+          <t>-0.004105665181413065 +/- 0.001896037047562891</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.010216422660725644 +/- 0.0013386213141192572</t>
+          <t>0.005346912794398528 +/- 0.0020909061369391198</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.0015276893698281447 +/- 0.001043998692988957</t>
+          <t>0.0030872056015277425 +/- 0.0011741481060278012</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0.00467854869509865 +/- 0.0007538331815612514</t>
+          <t>0.00038192234245706393 +/- 0.0011891496939700388</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-0.0005410566518141424 +/- 0.0005141786894145082</t>
+          <t>0.0003182686187142014 +/- 0.0003182686187142014</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>-0.000222788033099941 +/- 0.0011211912764996122</t>
+          <t>0.004996817313812907 +/- 0.0010656059225195992</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.001814131126670926 +/- 0.001156765235225078</t>
+          <t>0.0017504774029281078 +/- 0.0010769525344168673</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-0.0007956715467854925 +/- 0.0019003062047776294</t>
+          <t>-0.004678548695098606 +/- 0.0017260021467799076</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-0.0013367281985996126 +/- 0.001765171817168937</t>
+          <t>-0.003819223424570284 +/- 0.0016720465355268901</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>0.000668364099299823 +/- 0.0003002540143875494</t>
+          <t>-0.0008274984086568237 +/- 0.00032457157947756956</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.000652256573262878</t>
+          <t>-0.00012730744748565837 +/- 0.00043172055907860407</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.00012730744748568057 +/- 0.00015591914339804132</t>
+          <t>-0.000286441756842748 +/- 0.0002643737703028918</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.001559516231699576 +/- 0.0007724163653412784</t>
+          <t>0.0006047103755569938 +/- 0.0013080027108869846</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.005346912794398484 +/- 0.0014571003363793341</t>
+          <t>0.005951623169955467 +/- 0.0010268787908912676</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2951,92 +2951,92 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>-3.182686187142014e-05 +/- 0.0003884963595077644</t>
+          <t>0.0002864417568428035 +/- 0.0009382178849766647</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>0.0003819223424570417 +/- 0.0009943029504655401</t>
+          <t>0.0009229789942712064 +/- 0.0013080027108869794</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-3.182686187142014e-05 +/- 0.0011689603865186087</t>
+          <t>-0.0025461489497135004 +/- 0.0013502993911901253</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.0002864417568427813 +/- 0.00043754701097606006</t>
+          <t>-0.000318268618714157 +/- 0.0004025814971569829</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.0007320178230426633 +/- 0.0005702251071664319</t>
+          <t>0.003596435391470454 +/- 0.0016417848983486896</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>0.0006047103755569605 +/- 0.0017283480563189651</t>
+          <t>0.0019414385741566176 +/- 0.0016005462712514616</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>0.006047103755569705 +/- 0.0009333468044949159</t>
+          <t>0.005537873965627027 +/- 0.0014805478484548602</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>0.0028644175684277573 +/- 0.0014515282305526814</t>
+          <t>0.004646721833227274 +/- 0.0014247631626734068</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>-6.365372374284028e-05 +/- 0.00023817042563806617</t>
+          <t>-0.00022278803309990768 +/- 0.000428186634216191</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.003150859325270505 +/- 0.0007180467328248319</t>
+          <t>-0.0018459579885422572 +/- 0.0007088178692336268</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.001113940165499705 +/- 0.0005737669120725755</t>
+          <t>0.0005410566518141535 +/- 0.0008426608717297109</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.365372374284028e-05 +/- 0.0007504663349810212</t>
+          <t>-0.002928071292170542 +/- 0.00037116180107227384</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.0027371101209420767 +/- 0.0009983696461717203</t>
+          <t>0.003437301082113364 +/- 0.0011189303520844657</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>3.182686187142014e-05 +/- 0.0013461671535682394</t>
+          <t>0.002036919159770889 +/- 0.0010478725418939956</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>0.002832590706556337 +/- 0.0009700668780476096</t>
+          <t>-0.00197326543602796 +/- 0.0014846472042890659</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>0.0003182686187142014 +/- 0.0003486458036315579</t>
+          <t>-0.0009548058561424932 +/- 0.00024652981198010804</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>0.0002864417568427813 +/- 0.00046011560454491606</t>
+          <t>1.1102230246251566e-17 +/- 0.00034864580363153764</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>9.548058561426043e-05 +/- 0.0004512236434996219</t>
+          <t>0.00031826861871421254 +/- 0.0003765805081539973</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3046,52 +3046,52 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>-0.00041374920432846185 +/- 0.00042818663421623145</t>
+          <t>-0.00041374920432842857 +/- 0.0007123815813366835</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>0.0029598981540420065 +/- 0.0013803468136347119</t>
+          <t>2.2204460492503132e-17 +/- 0.0009548058561425673</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>3.182686187142014e-05 +/- 9.548058561426043e-05</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.000445576066199882 +/- 0.00040758270130063543</t>
+          <t>-0.0006047103755569272 +/- 0.00041374920432841485</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>-0.0009229789942711731 +/- 0.0011337691362544207</t>
+          <t>3.1826861871464554e-05 +/- 0.0009595680096550561</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>0.0019732654360280375 +/- 0.0006943801473351776</t>
+          <t>0.0024188415022279195 +/- 0.0018839781778419947</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>-6.365372374284028e-05 +/- 0.00027746014917509636</t>
+          <t>-0.0005092297899426778 +/- 0.0005363558098775142</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>0.0021642266072565476 +/- 0.0006333465544917789</t>
+          <t>-0.0010821133036282072 +/- 0.0008681210500945569</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>-0.002577975811584976 +/- 0.000521999346494452</t>
+          <t>-0.008847867600254578 +/- 0.0009091570246394652</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>0.0019096117122851864 +/- 0.0008540043198598662</t>
+          <t>0.00019096117122853197 +/- 0.0008563732684324398</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.011755285073670674 +/- 0.0014820929277718608</t>
+          <t>0.0007687379884689261 +/- 0.0012828305185458707</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3111,157 +3111,157 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.002017937219730981 +/- 0.001922111875551253</t>
+          <t>0.0076553491351697535 +/- 0.0012606450130784378</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0042280589365790485 +/- 0.0018720870206537401</t>
+          <t>0.003203074951953855 +/- 0.001811932815340289</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.007142857142857184 +/- 0.0010134075605096838</t>
+          <t>-0.002850736707238988 +/- 0.0012108301198869786</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.0021460602178091314 +/- 0.001249199231262014</t>
+          <t>0.0036194746957078695 +/- 0.0015431376643748975</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.009481101857783458 +/- 0.002091585870251709</t>
+          <t>-0.0016015374759769552 +/- 0.002095506372043067</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.203074951956264e-05 +/- 0.0005253433525578699</t>
+          <t>9.60922485586213e-05 +/- 0.00014678333423946444</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.0020179372197309696 +/- 0.001670826567039694</t>
+          <t>-0.001441383728379253 +/- 0.0017558577929104164</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-0.0072389493914157945 +/- 0.0018187148707979966</t>
+          <t>-0.00826393337604101 +/- 0.0027019982971125006</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.016752081998718794 +/- 0.0033899672291173005</t>
+          <t>-0.008744394618834094 +/- 0.003085776644234809</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.003203074951953833 +/- 0.0018288407973889025</t>
+          <t>0.0027226137091607705 +/- 0.0011026210427968338</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-0.0025304292120435943 +/- 0.0019189065728059016</t>
+          <t>-0.003907751441383745 +/- 0.0017879930476557189</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.0024983984625239985 +/- 0.001600255733093762</t>
+          <t>0.0008648302370275363 +/- 0.001707272001439648</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>9.609224855857689e-05 +/- 0.0026023875204291692</t>
+          <t>-0.006982703395259482 +/- 0.003281549897467176</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.0042921204356182185 +/- 0.0026844749314230633</t>
+          <t>-0.010185778347213337 +/- 0.001534804426740656</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.005989750160153717 +/- 0.002071129168523662</t>
+          <t>0.0007687379884689149 +/- 0.0012339116133413123</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.010762331838564999 +/- 0.0025269805154793067</t>
+          <t>0.0025624599615630683 +/- 0.0020509686859170023</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-0.007527226137091647 +/- 0.0018246284905350466</t>
+          <t>-0.000672645739910338 +/- 0.0013085649081240054</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.013709160794362551 +/- 0.00208962286102499</t>
+          <t>0.0069186418962203676 +/- 0.0022015170118436433</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-0.0001601537475977133 +/- 0.0005214228249871818</t>
+          <t>-0.00022421524663678304 +/- 0.0003219050487226591</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.017392696989109512 +/- 0.001777923009145163</t>
+          <t>0.016688020499679667 +/- 0.0020179372197309474</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.009064702114029433 +/- 0.0019221118755512513</t>
+          <t>-0.0062459961563100744 +/- 0.0016781789746867129</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.0011851377322229073 +/- 0.0015695067264574034</t>
+          <t>-0.002626521460602216 +/- 0.0017296604740550969</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.003299167200512465 +/- 0.0007450162299559976</t>
+          <t>0.0026265214606021603 +/- 0.0013034586770900628</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.0007687379884689594 +/- 0.001044811430512503</t>
+          <t>-0.004772581678411292 +/- 0.0019820279954394647</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.0006726457399103492 +/- 0.0008528844942789491</t>
+          <t>0.0003523382447149448 +/- 0.00026606738830616623</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>-0.004996796925048075 +/- 0.002076818075265522</t>
+          <t>-0.008904548366431796 +/- 0.0027246854988003644</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0.010089686098654682 +/- 0.002154648309909314</t>
+          <t>-0.00797565663036518 +/- 0.0009110482161004365</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>0.01710442024343366 +/- 0.0019068387016191093</t>
+          <t>-0.005893657911595152 +/- 0.0012339116133413305</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-0.009256886611146731 +/- 0.0015391433410293259</t>
+          <t>-0.006085842408712361 +/- 0.0007714025995382534</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-3.203074951956264e-05 +/- 0.0006317451288698259</t>
+          <t>-0.00019218449711725372 +/- 0.0007332173697796236</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.0008968609865470656 +/- 0.0006210992770552487</t>
+          <t>-0.00048046124279310654 +/- 0.00041144242724746325</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -3271,122 +3271,122 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.011723254324151212 +/- 0.0016155695340062289</t>
+          <t>-0.004196028187059597 +/- 0.0014285139731568068</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.0011210762331838931 +/- 0.0018133478353258442</t>
+          <t>-0.01278026905829598 +/- 0.0011676954601895155</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>-0.0014093529788597459 +/- 0.0008377128014492028</t>
+          <t>-0.00016015374759770218 +/- 0.0009635880177124364</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-0.0011851377322229738 +/- 0.0006877293578982635</t>
+          <t>0.00022421524663676084 +/- 0.0011100399392161041</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.002786675208199896 +/- 0.0008719191280471779</t>
+          <t>-0.004804612427930832 +/- 0.001418061731017197</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>-0.003042921204356219 +/- 0.0012259871370278541</t>
+          <t>0.002306213965406778 +/- 0.0016692907393716155</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-0.0014734144778988157 +/- 0.0010249839846252467</t>
+          <t>0.0009288917360666171 +/- 0.0008882398862179448</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.002370275464445859 +/- 0.001577006229992484</t>
+          <t>0.007078795643818037 +/- 0.0009867342601376985</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.002338244714926352 +/- 0.0020005761011694058</t>
+          <t>-0.0027866752081998846 +/- 0.002056214458129938</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>-0.013484945547725868 +/- 0.0023687600121056066</t>
+          <t>-0.006886611146700838 +/- 0.0017263950004115013</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-0.008392056374119172 +/- 0.0020649277977304605</t>
+          <t>-0.004804612427930832 +/- 0.0015361407826113883</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.008295964125560518 +/- 0.001709674073681288</t>
+          <t>-0.00032030749519540436 +/- 0.0014467123370449958</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.007046764894298496 +/- 0.0010623397791016777</t>
+          <t>0.003971812940422781 +/- 0.0011566604795174601</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>0.0015374759769378188 +/- 0.0012471442878880003</t>
+          <t>-0.0001601537475977133 +/- 0.0010838516537917183</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>0.0007687379884688706 +/- 0.0002935666684789119</t>
+          <t>0.0008327994875079958 +/- 0.0007046764894298442</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>-0.000960922485586202 +/- 0.0011459669327353286</t>
+          <t>0.0018898142216527748 +/- 0.0009762812718852019</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>-0.011499039077514438 +/- 0.0017394201130538699</t>
+          <t>-0.009385009609224882 +/- 0.0013817844080796244</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-0.0004484304932735661 +/- 0.0010545853704775233</t>
+          <t>-0.012203715566944296 +/- 0.0011588758818145898</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.00400384368994231 +/- 0.0017848343005451815</t>
+          <t>0.0027866752081998625 +/- 0.0019327578272319687</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>0.0008648302370275029 +/- 0.0006085842408712309</t>
+          <t>-0.0010249839846252717 +/- 0.0005871333369578238</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>-0.0011851377322229517 +/- 0.0007982021649184488</t>
+          <t>0.0006406149903907643 +/- 0.0004750927922546669</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.00044843049327351057 +/- 0.00021246795582029402</t>
+          <t>-3.203074951954044e-05 +/- 0.0004630631740807725</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-0.009865470852017954 +/- 0.0017117731218305495</t>
+          <t>0.0037796284433055495 +/- 0.0019314302923358606</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.005156950672645777 +/- 0.0014639839695101205</t>
+          <t>3.203074951952933e-05 +/- 0.0022258490266613457</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3396,92 +3396,92 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>0.0005124919923125915 +/- 0.0004344862256966679</t>
+          <t>-0.0015054452274183227 +/- 0.000497250951193449</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-0.004644458680333152 +/- 0.0008007687379884953</t>
+          <t>0.00041639974375399234 +/- 0.0015364746899694341</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>0.0018577834721332342 +/- 0.0025496154698440025</t>
+          <t>-0.010185778347213337 +/- 0.0016631332460918823</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.0008327994875079847 +/- 0.0006438100974452718</t>
+          <t>0.0004484304932735328 +/- 0.0004793923621747343</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-0.0026585522101217453 +/- 0.001289610643126019</t>
+          <t>0.011979500320307479 +/- 0.0009630555014972735</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-0.0014734144778988268 +/- 0.0010642695532246007</t>
+          <t>0.00855221012171683 +/- 0.0016209584790365058</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-0.0013452914798206539 +/- 0.0011441749583274762</t>
+          <t>-0.0001921844971172426 +/- 0.0022521967753039002</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>0.005477258167841092 +/- 0.0013318784680519994</t>
+          <t>0.004131966688020483 +/- 0.0014639839695101177</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>0.00012812299807816175 +/- 0.000156917984803543</t>
+          <t>0.0001921844971172426 +/- 0.00021246795582034422</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.007815502882767422 +/- 0.0012586087574880537</t>
+          <t>0.006662395900064055 +/- 0.0016066542221633102</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>-0.0018257527226137383 +/- 0.0014184234353289153</t>
+          <t>-0.001889814221652819 +/- 0.0013623427494001616</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.00041639974375395905 +/- 0.0006414152592729153</t>
+          <t>0.00038436899423446305 +/- 0.00044843049327352965</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.01688020499679691 +/- 0.001938058873466465</t>
+          <t>0.018001281229980782 +/- 0.0018277184647901565</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>-3.203074951958484e-05 +/- 0.0010570147341447892</t>
+          <t>-0.0021780909673286717 +/- 0.0008077847670031074</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>0.012459961563100553 +/- 0.0018811078616304963</t>
+          <t>0.023158231902626492 +/- 0.002026055682366248</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>-9.60922485586213e-05 +/- 0.00014678333423946444</t>
+          <t>0.0006406149903907865 +/- 0.00020258024728814843</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>0.0022741832158872264 +/- 0.0009442282493903792</t>
+          <t>-0.0002882767456758639 +/- 0.00033441084269414146</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>0.0008007687379884221 +/- 0.0005774425489212082</t>
+          <t>0.0005445227418321319 +/- 0.0005557127345578759</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>0.00035233824471490036 +/- 0.00048471319508075163</t>
+          <t>0.0006726457399103159 +/- 0.0005809851744784344</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>-0.0006726457399103492 +/- 0.0013623427494001816</t>
+          <t>3.203074951951823e-05 +/- 0.0019242457778187792</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3506,37 +3506,37 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>0.0011210762331838263 +/- 0.0008859267575874114</t>
+          <t>-0.00012812299807816175 +/- 0.0002935666684789289</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.0005765534913516612 +/- 0.0010984258936247325</t>
+          <t>-0.0010890454836643415 +/- 0.0012748077349220047</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>0.009256886611146663 +/- 0.0020381727443860398</t>
+          <t>0.002210121716848168 +/- 0.0011137308552667373</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>-0.00025624599615634567 +/- 0.0008922734322347135</t>
+          <t>-0.002049967969250499 +/- 0.0006595535003835395</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>0.004452274183215843 +/- 0.0020381727443860367</t>
+          <t>0.0001921844971172204 +/- 0.001726097832838883</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>0.013100576553491316 +/- 0.0021123301849836607</t>
+          <t>-0.00012812299807818395 +/- 0.0018906283873636974</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>0.0006726457399102825 +/- 0.0012687573555629965</t>
+          <t>-6.406149903909197e-05 +/- 0.0009036986534058817</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.0044843049327354615 +/- 0.0014108081707588172</t>
+          <t>0.0016015374759769218 +/- 0.001281229980781562</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3556,157 +3556,157 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.00022421524663674975 +/- 0.0012655186588813696</t>
+          <t>0.0064702114029468235 +/- 0.0019207769827757923</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.005124919923126148 +/- 0.0021343153425954736</t>
+          <t>0.0032991672005124872 +/- 0.002578624543571894</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.00041639974375404785 +/- 0.00153647468996944</t>
+          <t>-0.0062459961563100744 +/- 0.001148202967901018</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.011819346572709777 +/- 0.001667138203673695</t>
+          <t>0.013709160794362584 +/- 0.002094526934563975</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.015278667520819966 +/- 0.001969565552805045</t>
+          <t>-0.0031069827033952556 +/- 0.0019799563690615714</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0010570147341447233 +/- 0.0002501681510540379</t>
+          <t>0.00012812299807816175 +/- 0.0002562459961563235</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0025624599615630683 +/- 0.000894570150145359</t>
+          <t>0.0016976297245355654 +/- 0.0010724323537977612</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.03148622677770656 +/- 0.002781516058983254</t>
+          <t>0.022773862908392062 +/- 0.001870167915053814</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.0493593850096092 +/- 0.003057049369042357</t>
+          <t>0.03350416399743755 +/- 0.0029293692159317476</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.0006726457399102825 +/- 0.0007367072389493847</t>
+          <t>-0.0011210762331838487 +/- 0.0014625816856926228</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.0049967969250480195 +/- 0.0016900584187409158</t>
+          <t>0.004612427930813567 +/- 0.0025592548821829616</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.012652146060217773 +/- 0.0013532754756103594</t>
+          <t>0.002754644458680322 +/- 0.0030258464262958498</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.008584240871236359 +/- 0.001753226416835871</t>
+          <t>0.0032351057014734174 +/- 0.0023382447149263444</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.0023382447149262963 +/- 0.0017836842783249133</t>
+          <t>-0.005124919923126203 +/- 0.002526168373239006</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.004292120435618163 +/- 0.0009945019023869428</t>
+          <t>-0.0016335682254964845 +/- 0.0013623427494001807</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.0012491992312619992 +/- 0.0011851377322229311</t>
+          <t>0.0020499679692504657 +/- 0.0013604587175909857</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>-0.0023062139654068336 +/- 0.0011881638046759395</t>
+          <t>-0.0007687379884689149 +/- 0.0017555656125617907</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>-0.003939782190903307 +/- 0.0009398719251198744</t>
+          <t>0.00832799487508008 +/- 0.00208569129994872</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.00041639974375397016 +/- 0.0004064246489573569</t>
+          <t>0.00016015374759770218 +/- 0.00038570129976915206</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.006630365150544504 +/- 0.0019695655528050205</t>
+          <t>0.006982703395259471 +/- 0.00160025573309377</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>-0.005509288917360677 +/- 0.0014166139902303703</t>
+          <t>-0.004644458680333108 +/- 0.001537809594382805</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.0023382447149262963 +/- 0.0012735999584927</t>
+          <t>0.0003523382447149337 +/- 0.0009550321278588054</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>-0.0008327994875080291 +/- 0.0016900584187409193</t>
+          <t>-0.0019218449711723262 +/- 0.0012070111262919032</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.006694426649583573 +/- 0.0016234882636097776</t>
+          <t>0.0020179372197309474 +/- 0.0014038825753242073</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>3.203074951951823e-05 +/- 0.00058098517447844</t>
+          <t>-0.0003843689942344741 +/- 0.0005124919923126276</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.013420884048686698 +/- 0.002381718314544694</t>
+          <t>-0.003042921204356175 +/- 0.0013456727442408588</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0.001697629724535521 +/- 0.0028471354719619185</t>
+          <t>-0.006566303651505445 +/- 0.0017616912235746361</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>-0.00448430493273545 +/- 0.0012238932206625668</t>
+          <t>-0.008904548366431763 +/- 0.0010984258936247377</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-0.003715566944266535 +/- 0.001702156342804171</t>
+          <t>-0.006213965406790511 +/- 0.0014410277872135913</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-0.0014093529788597348 +/- 0.0004344862256966645</t>
+          <t>0.00022421524663678304 +/- 0.00045411424980008224</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.0002562459961563235 +/- 0.0003449817301175392</t>
+          <t>-0.0006406149903907865 +/- 0.0005164803169954086</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -3716,122 +3716,122 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.002562459961563135 +/- 0.001145966932735307</t>
+          <t>-0.003139013452914774 +/- 0.0015481160760531139</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.0037155669442664797 +/- 0.0018187148707979844</t>
+          <t>-0.0010249839846252385 +/- 0.001822096432200879</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>-0.00032030749519540436 +/- 0.0003789929393401618</t>
+          <t>-0.0021780909673286388 +/- 0.0006374038674609937</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-0.00089686098654711 +/- 0.0005693910581239929</t>
+          <t>0.0008648302370275806 +/- 0.0004972509511934617</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.006117873158231879 +/- 0.0011937633025998985</t>
+          <t>0.003747597693786042 +/- 0.0017311427439937882</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>-0.0010890454836643304 +/- 0.0005940819023379503</t>
+          <t>-0.005124919923126192 +/- 0.0019951840489939037</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-0.0015695067264574146 +/- 0.0008882398862179404</t>
+          <t>-0.002914798206278035 +/- 0.0005809851744784344</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.0033632286995515237 +/- 0.000920013236152797</t>
+          <t>0.00451633568225498 +/- 0.0009970776692039202</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.001985906470211385 +/- 0.0009480236122324644</t>
+          <t>-0.0038436899423446524 +/- 0.0012238932206625785</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-0.0004484304932735661 +/- 0.0014267173255169744</t>
+          <t>-0.0001921844971172426 +/- 0.001714168886644423</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-0.01726457399103143 +/- 0.0020879037139951606</t>
+          <t>-0.0407431133888533 +/- 0.0030816178016158254</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>-0.005188981422165295 +/- 0.001827718464790136</t>
+          <t>-0.004612427930813567 +/- 0.0008736823636762298</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0065342729019858825 +/- 0.0009415079088212173</t>
+          <t>-0.001761691223574635 +/- 0.0015510954532739348</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0.00861627162075589 +/- 0.0013921405388917858</t>
+          <t>-0.005637411915438817 +/- 0.0020217468082074927</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-0.00048046124279310654 +/- 0.0006907065551841073</t>
+          <t>0.00032030749519539324 +/- 0.0006243942565540812</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>-0.004516335682255001 +/- 0.0018088158748873176</t>
+          <t>0.003875720691864182 +/- 0.001774457268989684</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>-0.02014734144778989 +/- 0.0019242457778187963</t>
+          <t>-0.012171684817424722 +/- 0.0015159717573605676</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-0.03215887251761694 +/- 0.0033139057415445417</t>
+          <t>-0.0353619474695708 +/- 0.002858463999657023</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-0.023959000640615034 +/- 0.0020449570402962516</t>
+          <t>-0.0325752722613709 +/- 0.0018008575012005976</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>0.0003523382447149226 +/- 0.00048471319508075754</t>
+          <t>-0.0008968609865470766 +/- 0.0012388904295844722</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>-0.00022421524663679415 +/- 0.0005369332035310868</t>
+          <t>0.0010570147341447899 +/- 0.0002050968685916614</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>-0.0023702754644458813 +/- 0.0004101937371834199</t>
+          <t>-0.0003523382447149337 +/- 0.0008284764353861572</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-0.038853299167200525 +/- 0.002296629310729453</t>
+          <t>-0.04647661755285074 +/- 0.002298415528623989</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.014606021780909684 +/- 0.0013528963537439455</t>
+          <t>-0.021044202434336957 +/- 0.0020005761011693884</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3841,92 +3841,92 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-0.000288276745675875 +/- 0.0008766132084179598</t>
+          <t>-0.00041639974375401456 +/- 0.0005174725951762833</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>0.0035554131966687775 +/- 0.0013698529647881588</t>
+          <t>0.006181934657270971 +/- 0.001823503565341486</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-0.01857783472133251 +/- 0.0014955307533540906</t>
+          <t>-0.014381806534272911 +/- 0.002364424796151245</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.0009288917360665949 +/- 0.0008766132084179403</t>
+          <t>0.0008327994875080181 +/- 0.0006438100974452729</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.0016655989750159917 +/- 0.0008203874743667964</t>
+          <t>-0.00714285714285714 +/- 0.0022921576762094525</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-0.022741832158872533 +/- 0.002287453052063703</t>
+          <t>-0.02158872517616911 +/- 0.002502501599567557</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>0.0009929532351056758 +/- 0.0014986146784483887</t>
+          <t>-0.003971812940422803 +/- 0.0021400759882754515</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-0.0005765534913517278 +/- 0.0016507493564029696</t>
+          <t>-0.004676489429852648 +/- 0.0013604587175909946</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>0.0007687379884689039 +/- 0.0007740580380265546</t>
+          <t>-0.0005124919923126248 +/- 0.0007470790384170856</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>-0.0007687379884689482 +/- 0.0013299512807191905</t>
+          <t>-0.006566303651505445 +/- 0.001863573120792919</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>-0.008744394618834117 +/- 0.0015497719927486334</t>
+          <t>-0.010121716848174245 +/- 0.0011387821162479777</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.0005124919923125915 +/- 0.0006595535003835223</t>
+          <t>-0.0017937219730941756 +/- 0.0012087099464518254</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-0.007943625880845618 +/- 0.0023528978439727004</t>
+          <t>-0.006085842408712361 +/- 0.0021677033075834054</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>0.0073670723894939 +/- 0.001388820204271568</t>
+          <t>0.0005765534913516945 +/- 0.0018051252791294505</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>-0.00570147341447792 +/- 0.0018051252791294358</t>
+          <t>-0.00121716848174247 +/- 0.002236654740563238</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>-0.0002562459961563235 +/- 0.00019218449711724264</t>
+          <t>-0.0002882767456758639 +/- 0.0003021774866129756</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>0.00032030749519534885 +/- 0.0008474539753570057</t>
+          <t>-0.0027546444586803442 +/- 0.0007740580380265629</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>0.0009929532351056647 +/- 0.0006634309794108968</t>
+          <t>-0.0006406149903907754 +/- 0.0006718826701922745</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3936,52 +3936,52 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>0.00016015374759766887 +/- 0.0009200132361527988</t>
+          <t>-0.0014093529788597014 +/- 0.0008498718232813133</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>0.004708520179372166 +/- 0.0016460813782869447</t>
+          <t>0.002498398462524032 +/- 0.0015281051174729698</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>-6.406149903908087e-05 +/- 0.00012812299807816175</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>0.0005445227418321208 +/- 0.0005174725951762621</t>
+          <t>0.000512491992312647 +/- 0.00029356666847892894</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>-0.0032991672005124985 +/- 0.0012573854212934484</t>
+          <t>-0.0015054452274183227 +/- 0.0018679722372611598</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>0.00012812299807812844 +/- 0.001120618557625611</t>
+          <t>-0.005637411915438828 +/- 0.0018577834721332468</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>0.0017296604740550726 +/- 0.0005204380784520427</t>
+          <t>0.00012812299807815064 +/- 0.0008253746782014748</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>0.0011851377322229073 +/- 0.0012074360554113093</t>
+          <t>-0.005637411915438828 +/- 0.0021304662585926635</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>0.0004484304932735328 +/- 0.0022061723712649105</t>
+          <t>-0.005253042921204343 +/- 0.0017672151472304806</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>-0.00342729019859066 +/- 0.0007024891799955464</t>
+          <t>0.0007046764894298562 +/- 0.000845029209370463</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.001368457064659545 +/- 0.0018486836929327804</t>
+          <t>-0.000376325692781454 +/- 0.0010974351647174418</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4001,157 +4001,157 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.0011973999315771033 +/- 0.0024154817801031745</t>
+          <t>0.0008552856654121865 +/- 0.002154233526025469</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0018132056106739403 +/- 0.0007808903325701867</t>
+          <t>0.0022237427300717872 +/- 0.0013272093562279018</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.001505302771125505 +/- 0.001598812377084888</t>
+          <t>0.0032500855285664708 +/- 0.0014291206687790333</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.003557988368114995 +/- 0.0014691009615863029</t>
+          <t>-0.00660280533698262 +/- 0.0014109880689224473</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0006500171057132742 +/- 0.001578552445440892</t>
+          <t>0.0007526513855627082 +/- 0.0015053027711255476</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6.842285323296337e-05 +/- 0.00036846834123396616</t>
+          <t>0.00017105713308240844 +/- 0.00027582133931911804</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0010605542251111543 +/- 0.0010867177676543726</t>
+          <t>-0.003010605542251166 +/- 0.000806693542425708</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.03130345535408822 +/- 0.0024682068402911636</t>
+          <t>0.021861101607937007 +/- 0.002077904158612419</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.021313718782073186 +/- 0.0024814488957630577</t>
+          <t>0.024563804310639703 +/- 0.0019401227340072333</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-0.0004447485460144174 +/- 0.0009057955726906497</t>
+          <t>-0.007321245295928891 +/- 0.001290999812802803</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.0018132056106739292 +/- 0.001038247752685161</t>
+          <t>0.0005815942524802886 +/- 0.0011143686264045289</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.0023263770099212766 +/- 0.0007771342245364687</t>
+          <t>-0.0003763256927814429 +/- 0.0011495242980781176</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.01700307902839545 +/- 0.004605346005186364</t>
+          <t>0.004242216900444684 +/- 0.0037263766826384115</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.015668833390352334 +/- 0.0021841792267550215</t>
+          <t>0.01388983920629484 +/- 0.0019182820073727134</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>-0.00013684570646599337 +/- 0.0015467197475822392</t>
+          <t>-0.000650017105713363 +/- 0.0017272535834915346</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-0.001984262743756471 +/- 0.000876240059860816</t>
+          <t>-0.0037974683544304334 +/- 0.0008848797233238188</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.0026684912760861603 +/- 0.0006977789276213119</t>
+          <t>0.0010605542251111212 +/- 0.0013637448804649011</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>-0.0007526513855628192 +/- 0.0015885305188154482</t>
+          <t>-0.0029079712624016985 +/- 0.001930749375234009</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-3.3306690738754695e-17 +/- 0.0003421142661648835</t>
+          <t>-0.00010263427984950058 +/- 0.0002671997836437301</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.00400273691412929 +/- 0.0012986830582348498</t>
+          <t>0.00037632569278132075 +/- 0.001793736124381563</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.001094765651727636 +/- 0.0014254304930550823</t>
+          <t>-0.005097502565857071 +/- 0.0008980092198704528</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>-0.0004105371193979357 +/- 0.0005255659081675533</t>
+          <t>-0.0020184741703729637 +/- 0.0011495242980781018</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.0006158056790967814 +/- 0.0014498542661934325</t>
+          <t>0.0005473828258637847 +/- 0.0011771912784184107</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.0002736914129318757 +/- 0.0010796944124570362</t>
+          <t>-0.0019500513171399891 +/- 0.0015303639580119923</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.00037632569278133187 +/- 0.0003571777799832513</t>
+          <t>-0.0010947656517277249 +/- 0.0006454999064014218</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.004310639753677692 +/- 0.0017657869176276211</t>
+          <t>0.00034211426616485017 +/- 0.002605464627391009</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0.00010263427984942286 +/- 0.0010382477526851733</t>
+          <t>-0.004686965446459179 +/- 0.0011248225947843823</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>-0.00041053711939790236 +/- 0.0011011616106350417</t>
+          <t>-0.0021895313034554055 +/- 0.0008124763658595974</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0027711255559356497 +/- 0.0010427472223146108</t>
+          <t>-0.005165925419090045 +/- 0.0011289770783441655</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>-0.00010263427984950058 +/- 0.0005527025118509457</t>
+          <t>0.0006158056790967703 +/- 0.0005255659081675143</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.00010263427984944507 +/- 0.0002671997836437231</t>
+          <t>0.00044474854601431744 +/- 0.0002671997836437302</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -4161,272 +4161,272 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.002292165583304784 +/- 0.0010382477526851557</t>
+          <t>-0.0023263770099213655 +/- 0.0010009400505184966</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.0016763599042080358 +/- 0.0017474639465100417</t>
+          <t>-0.004310639753677792 +/- 0.0013955578552426351</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>0.0007184399589462487 +/- 0.0003885671122682485</t>
+          <t>-0.0011973999315771922 +/- 0.0006167552643626451</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>6.842285323295227e-05 +/- 0.0005255659081675388</t>
+          <t>0.00047895997263079914 +/- 0.0005120297484466446</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.0023605884365378695 +/- 0.0010649594537306558</t>
+          <t>-0.0021553198768389124 +/- 0.0015755838439506674</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>0.0010263427984946616 +/- 0.0015223123818875765</t>
+          <t>-0.0017447827574410212 +/- 0.0007249271330967118</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.0011289770783441178 +/- 0.000750315162485844</t>
+          <t>0.0008210742387957049 +/- 0.0008681886787854621</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.0011973999315772032 +/- 0.001485343369558148</t>
+          <t>-0.0006842285323298448 +/- 0.0009676452701834178</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.002394799863154262 +/- 0.0012616550745525505</t>
+          <t>-0.002497434143003796 +/- 0.0009312800266039099</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>-0.0015395141977420756 +/- 0.0010845615794832428</t>
+          <t>0.004960656859390978 +/- 0.0012071350505903262</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.0008210742387957271 +/- 0.0008546011629693318</t>
+          <t>-0.006602805336982609 +/- 0.0012621188330958848</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>-0.0029421826890181912 +/- 0.0011159429647827391</t>
+          <t>-0.008655490933971999 +/- 0.0014679054363958143</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.007287033869312287 +/- 0.0011454443409362387</t>
+          <t>-0.0033185083817995676 +/- 0.0011556172257307354</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.0005473828258638847 +/- 0.0007831353501375247</t>
+          <t>0.002052685596989334 +/- 0.0009306514203719012</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>6.842285323293007e-05 +/- 0.0003352021543322687</t>
+          <t>-0.0004105371193979135 +/- 0.0005885956392092225</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>0.005713308244953763 +/- 0.001360307584814998</t>
+          <t>-0.0014368799178926307 +/- 0.001366745422883219</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>-0.003968525487512875 +/- 0.0015841035788970407</t>
+          <t>-0.003523776941498513 +/- 0.0014679054363958305</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-0.0025658569962367928 +/- 0.0009585306689101496</t>
+          <t>-0.0005473828258638847 +/- 0.0013000342114266295</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-0.0005131713992473919 +/- 0.001547098057419759</t>
+          <t>-0.004002736914129379 +/- 0.0014026684912760731</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-0.0012316113581936849 +/- 0.00041053711939786723</t>
+          <t>0.0011289770783440955 +/- 0.0004340943393927192</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.0005473828258638069 +/- 0.0005120297484466565</t>
+          <t>0.0005815942524802886 +/- 0.0004602676718123086</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>-0.00047895997263089905 +/- 0.0002736914129319423</t>
+          <t>-0.00010263427984951168 +/- 0.0003763256927813813</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-0.006192268217584706 +/- 0.001832468250542886</t>
+          <t>-0.0013000342114266484 +/- 0.000525565908167546</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.0031816626753335296 +/- 0.0014679054363958086</t>
+          <t>-0.007971262401642198 +/- 0.0013516761043543366</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>3.4211426616481686e-05 +/- 0.00010263427984944506</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>-0.0013342456380431521 +/- 0.0005815942524803343</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>0.0027027027027026417 +/- 0.0008302881354438301</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>-0.010229216558330511 +/- 0.0014470260679135545</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>-0.0009579199452617537 +/- 0.0005255659081675431</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>-0.0006842285323298448 +/- 0.0010926253453760507</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-0.007526513855627826 +/- 0.0017037153059170401</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>0.0025316455696202 +/- 0.0014368799178925771</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-0.0013000342114266594 +/- 0.001024059496893313</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>-0.0008552856654123087 +/- 0.00035056280417242517</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>-0.006910708176531044 +/- 0.0007771342245364843</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>0.0011631885049605884 +/- 0.0011571354447682378</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>-0.0008894970920287681 +/- 0.0008947449080138278</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>-0.005815942524803353 +/- 0.001654928035914862</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>-0.00023947998631548283 +/- 0.001280531458926633</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>-0.002086897023605949 +/- 0.0015334201047564032</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>-0.00017105713308248615 +/- 0.0003824953776085778</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>-0.0009579199452617648 +/- 0.0006977789276213141</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>-0.0011973999315771922 +/- 0.00043945373173673703</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>0.0012658227848100889 +/- 0.000824630228750856</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>0.0030790283954840515 +/- 0.0011752010973190125</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>-0.005952788231269268 +/- 0.0011159429647827732</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.00023947998631538293 +/- 0.0005311041634026726</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0.003729045501197348 +/- 0.0013112396781893149</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-0.00013684570646600448 +/- 0.0015914749708673243</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>0.0008210742387957159 +/- 0.0008407940969855871</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>0.0028737598357851057 +/- 0.0012163112442443445</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>6.842285323295227e-05 +/- 0.0002982483026712561</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>-0.003250085528566593 +/- 0.0010291898020178861</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>-0.00266849127608626 +/- 0.0009530200668617375</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>0.0002736914129318646 +/- 0.0004789599726308563</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>0.0029079712624015984 +/- 0.001613749766003524</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>-0.0040027369141293675 +/- 0.0012896391943188912</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>0.0018132056106739292 +/- 0.0012339848646508082</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>0.00013684570646592674 +/- 0.0003809623238337222</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>3.421142661644838e-05 +/- 0.0005815942524803343</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>-0.0005473828258638735 +/- 0.0005964966053425454</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>0.00017105713308240844 +/- 0.000671276663371496</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>-0.004892234006158125 +/- 0.0008795730504401279</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>0.0019158398905234075 +/- 0.0007526513855627768</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>-0.004823811152925117 +/- 0.0011596613928620018</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>-0.00023947998631546064 +/- 0.00034382058231683846</t>
+          <t>0.0006158056790967592 +/- 0.0005473828258638222</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>-0.00010263427984950058 +/- 0.0007808903325701946</t>
+          <t>-0.004858022579541621 +/- 0.0014579046016190635</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>0.00044474854601433966 +/- 0.0011248225947843682</t>
+          <t>-0.0030790283954841625 +/- 0.0014675067115653188</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>-0.0004447485460144174 +/- 0.0005085894200245993</t>
+          <t>-0.0004447485460143952 +/- 0.0006500171057133121</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>-0.0014368799178926194 +/- 0.001202763998032626</t>
+          <t>-0.008552856654122531 +/- 0.0017644607537773054</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>-0.0011289770783442176 +/- 0.0006677804069771748</t>
+          <t>-0.00783441669517626 +/- 0.0011895544749034293</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>0.00010263427984943396 +/- 0.0008927805919055599</t>
+          <t>0.0014710913445090124 +/- 0.0005311041634026698</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.003889789303079483 +/- 0.0021206388633771313</t>
+          <t>-0.008233387358184796 +/- 0.0022184685422714564</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4446,157 +4446,157 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.0064829821717990125 +/- 0.0009938223479258295</t>
+          <t>-0.0020097244732577126 +/- 0.002281972889049999</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.006061588330632117 +/- 0.0009511442950483718</t>
+          <t>-0.014035656401944907 +/- 0.0019931875707803245</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.001329011345218789 +/- 0.001300237998063637</t>
+          <t>0.013484602917341947 +/- 0.0017225711838685723</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.011604538087520289 +/- 0.0022023063535122366</t>
+          <t>-0.01098865478119936 +/- 0.0014744331170883974</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.0023338735818476896 +/- 0.0015733758313791432</t>
+          <t>-0.0013290113452188335 +/- 0.0013242592036185167</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.00032414910858991064 +/- 0.0002050098969314737</t>
+          <t>-2.2204460492503132e-17 +/- 0.0003550875575398321</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-6.482982171802653e-05 +/- 0.0011115998832727458</t>
+          <t>-0.0008427876823339009 +/- 0.0011432863590631057</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.02855753646677469 +/- 0.0026312043920363806</t>
+          <t>0.008330632090761713 +/- 0.0026415666427072122</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.0009724473257698874 +/- 0.0031859092059139476</t>
+          <t>0.021847649918962698 +/- 0.003160079768415926</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-0.006677471636953025 +/- 0.002499103438236157</t>
+          <t>-0.0028525121555916023 +/- 0.0013889325955026655</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-0.004764991896272319 +/- 0.00178164098329481</t>
+          <t>-0.009789303079416545 +/- 0.001102106969205832</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-0.005251215559157252 +/- 0.001469793717828787</t>
+          <t>-0.009854132901134526 +/- 0.002004489443596798</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.014846029173419739 +/- 0.0035115987199872546</t>
+          <t>0.042949756888168523 +/- 0.0027245884718551682</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.006515397082657981 +/- 0.0030423427260557</t>
+          <t>0.0059967585089140685 +/- 0.0018691349424101748</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>-0.0021717990275527234 +/- 0.0018623769753287804</t>
+          <t>-0.00369529983792547 +/- 0.001134058715367</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.0031766612641815017 +/- 0.0016830800629818025</t>
+          <t>-0.005348460291734214 +/- 0.0019080794363385883</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-0.0009724473257699095 +/- 0.0011322041618523789</t>
+          <t>0.004149108589951345 +/- 0.0009483785308478515</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>-0.0017828200972447527 +/- 0.0011709816446151466</t>
+          <t>-0.00025931928687197294 +/- 0.0015733758313791495</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>9.724473257696208e-05 +/- 0.00020755670137545345</t>
+          <t>0.0002593192868719396 +/- 0.0004048621068653963</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.007585089141004831 +/- 0.0024222420346540394</t>
+          <t>0.008103727714748743 +/- 0.0017274440965282646</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.004667747163695279 +/- 0.001528664651222249</t>
+          <t>0.007001620745542924 +/- 0.0011247553693936633</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-0.004278768233387376 +/- 0.0015932843730884318</t>
+          <t>0.003176661264181513 +/- 0.0012111210173270154</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>-0.0029821717990275777 +/- 0.0020745542949757</t>
+          <t>-0.0035656401944894832 +/- 0.0012385720048326092</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.0033063209076175217 +/- 0.001270399866597431</t>
+          <t>0.0021393841166936546 +/- 0.0015217756362146423</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-3.241491085903547e-05 +/- 0.0005698021339139968</t>
+          <t>0.002009724473257679 +/- 0.0009029749288287895</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>-0.0016855753646677573 +/- 0.0013505780652187712</t>
+          <t>-0.0043435980551053575 +/- 0.0024048281349745766</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0.0025283630470015915 +/- 0.0012786439496477024</t>
+          <t>-6.482982171802653e-05 +/- 0.0020023915995436687</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0.005672609400324125 +/- 0.0008727981859213192</t>
+          <t>0.0008752025931928365 +/- 0.00111396047179511</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.004732576985413262 +/- 0.001734727800357785</t>
+          <t>-0.0012641815235008291 +/- 0.0023618439198634603</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>-0.0007455429497569277 +/- 0.0004595606767830739</t>
+          <t>-0.00032414910858997726 +/- 0.0005424052035877495</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-6.482982171803763e-05 +/- 0.0006285484418043931</t>
+          <t>-0.00022690437601300407 +/- 0.0004360980242163208</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -4606,122 +4606,122 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.002236628849270628 +/- 0.0014310366323918207</t>
+          <t>0.0012641815235007957 +/- 0.0014672895037609484</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.0022690437601296408 +/- 0.0006799409064311999</t>
+          <t>0.002042139384116648 +/- 0.0016275384389799813</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0.004376012965964316 +/- 0.0011709816446151236</t>
+          <t>0.0001620745542949442 +/- 0.0007704936352677461</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.0015235008103727243 +/- 0.0010657557356741265</t>
+          <t>0.0003565640194489017 +/- 0.0010193961227563395</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.006061588330632128 +/- 0.0011870232365381339</t>
+          <t>-0.0001944894651540019 +/- 0.001281926737976368</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>0.0034359805510534524 +/- 0.0012737039030397527</t>
+          <t>0.0010372771474878029 +/- 0.0016129472031928326</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>3.2414910858957756e-05 +/- 0.0007595056410930304</t>
+          <t>0.0008103727714748543 +/- 0.0008606754001524538</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.0008103727714748432 +/- 0.001115845347037827</t>
+          <t>0.0004538087520258971 +/- 0.0015491478956691888</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.008492706645056691 +/- 0.0018945399281948005</t>
+          <t>0.01374392220421391 +/- 0.001764753009895113</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.0011021069692058072 +/- 0.0024048281349745688</t>
+          <t>-0.0028849270664506044 +/- 0.0017543026421698233</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-0.0020745542949757168 +/- 0.0011615217417937631</t>
+          <t>-0.010113452188006512 +/- 0.0026445482080221737</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>-0.0035656401944894945 +/- 0.0019340594995366433</t>
+          <t>0.0014910858995137444 +/- 0.0018462276649462853</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.005899513776337073 +/- 0.001586675948203623</t>
+          <t>0.0011669367909238116 +/- 0.0008600647754568129</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>0.0039870340356563784 +/- 0.0010949332741688523</t>
+          <t>0.009789303079416523 +/- 0.001319091730915785</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-4.4408920985006264e-17 +/- 0.0003835383976077534</t>
+          <t>-0.0007131280388979255 +/- 0.0007504594426444429</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>0.0003565640194489017 +/- 0.0009219748883843053</t>
+          <t>-0.0010372771474878694 +/- 0.0007643323256111141</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>-0.0027876823338735977 +/- 0.0018001223179144115</t>
+          <t>-0.00654781199351705 +/- 0.001619448427461495</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-0.0109562398703404 +/- 0.001403981058522372</t>
+          <t>-0.0121231766612642 +/- 0.0018001223179144239</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-0.01730956239870344 +/- 0.0022042139384116604</t>
+          <t>-0.0075202593192868926 +/- 0.001645196439604454</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>0.0024635332252836207 +/- 0.0005834683954618873</t>
+          <t>-0.0001944894651539908 +/- 0.0009527998999480866</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.00035656401944891283 +/- 0.0006868596466909781</t>
+          <t>0.0008427876823338676 +/- 0.0006674638665145437</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>-0.00032414910858996615 +/- 0.0004348916649918504</t>
+          <t>0.00016207455429495532 +/- 0.00033215399565509387</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-0.021037277147487887 +/- 0.0010794700684179476</t>
+          <t>-0.004959481361426288 +/- 0.001787528775230109</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-0.0019773095623987214 +/- 0.001145581656212154</t>
+          <t>-0.0014586709886547978 +/- 0.002015206618135433</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4731,92 +4731,92 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>0.0011993517017827803 +/- 0.0006959776516559008</t>
+          <t>-0.0003241491085899884 +/- 0.0007532544595541415</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>0.006839546191247947 +/- 0.0012080807230848813</t>
+          <t>0.0020421393841166813 +/- 0.001305077610320744</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-0.0037925445705024653 +/- 0.001799246559011719</t>
+          <t>-0.002495948136142656 +/- 0.001383247215128151</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.0010048622366288118 +/- 0.0009219748883843063</t>
+          <t>-0.000551053484602948 +/- 0.000543372921045066</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-0.0009076175040519052 +/- 0.0014039810585223674</t>
+          <t>-0.004343598055105391 +/- 0.001507903189577052</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-0.018411669367909268 +/- 0.0014840224495636487</t>
+          <t>-0.013743922204213953 +/- 0.0015626542357463859</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-0.006029173419773148 +/- 0.00152866465122226</t>
+          <t>-0.005186385737439281 +/- 0.0016077272956417793</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>0.005024311183144203 +/- 0.0014658566035131552</t>
+          <t>0.0027552674230145514 +/- 0.0013695060080569123</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>0.0001620745542949442 +/- 0.00029885071174367216</t>
+          <t>0.00012965964343596424 +/- 0.0002593192868719701</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.007487844408427846 +/- 0.0010498628681168119</t>
+          <t>0.008687196110210672 +/- 0.0012703998665974452</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.0019124797406806838 +/- 0.0011905586821527993</t>
+          <t>0.00042139384116690604 +/- 0.0013368940439093427</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.000356564019448935 +/- 0.0011455816562121542</t>
+          <t>0.0016207455429497308 +/- 0.0010944533559892407</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.004829821717990246 +/- 0.0014528969096282178</t>
+          <t>0.01416531604538086 +/- 0.001665823683310147</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>0.0030145867098865242 +/- 0.0015949322009909171</t>
+          <t>0.011150729335494314 +/- 0.0009853279840240157</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>0.006256077795786019 +/- 0.0022130151298150303</t>
+          <t>0.013646677471636937 +/- 0.0025001543206837713</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>0.00022690437601293744 +/- 0.00014854378265657258</t>
+          <t>0.0002917341977309529 +/- 0.00026925847205570147</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>0.00223662884927065 +/- 0.0008988930064092056</t>
+          <t>0.0025283630470015806 +/- 0.0007913488243587587</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>-0.00016207455429499972 +/- 0.0009751448270010353</t>
+          <t>-0.000259319286871984 +/- 0.0012111210173270301</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4826,52 +4826,52 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>0.0028525121555915355 +/- 0.0005762200594694074</t>
+          <t>-0.0002917341977309751 +/- 0.000850852819993943</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>0.0041166936790923425 +/- 0.0011781382071563281</t>
+          <t>-0.0009076175040518941 +/- 0.0010925315751282247</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>-3.241491085900217e-05 +/- 9.72447325770065e-05</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>0.0004862236628848882 +/- 0.00041637706900049857</t>
+          <t>0.0007131280388978922 +/- 0.0007913488243587423</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.00074554294975685 +/- 0.001527633279474647</t>
+          <t>0.002917341977309551 +/- 0.0016207455429497664</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>0.009692058346839528 +/- 0.0011363726510831857</t>
+          <t>0.01128038897893029 +/- 0.0018778279880661479</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>-0.0007779578606158966 +/- 0.0007131280388978842</t>
+          <t>0.0007131280388978589 +/- 0.0008045169300480492</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>0.004376012965964293 +/- 0.0015082515558031587</t>
+          <t>0.00042139384116691715 +/- 0.001141906966211252</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>0.0005510534846028925 +/- 0.0010255618813326468</t>
+          <t>0.004181523500810358 +/- 0.0007595056410930318</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>-0.00589951377633714 +/- 0.0014114451252562042</t>
+          <t>-0.004376012965964371 +/- 0.0010069513495629672</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.0027392845633258723 +/- 0.0018526951146380485</t>
+          <t>-0.00145020947470188 +/- 0.001663668643137654</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4891,157 +4891,157 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.005027392845633305 +/- 0.0015197971153788539</t>
+          <t>0.005091846600064476 +/- 0.0016483031714526885</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.003996132774734063 +/- 0.001950724582716266</t>
+          <t>0.015082178536899794 +/- 0.001804705124073487</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.0041894940380277634 +/- 0.0013130228029302846</t>
+          <t>-0.006284241057041529 +/- 0.0018860296343408904</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.010087012568482167 +/- 0.0011443945152797043</t>
+          <t>0.002997099581050633 +/- 0.0011352829490047513</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.0005156300354496213 +/- 0.0017246649255893668</t>
+          <t>0.0060908797937480165 +/- 0.0016460963956328868</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-6.445375443124846e-05 +/- 0.00042753783955597256</t>
+          <t>-9.668063164676166e-05 +/- 0.00035449564937157385</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.008378988076055482 +/- 0.0017052860528937</t>
+          <t>0.0030937802126974278 +/- 0.0014852360453500477</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-0.01817595874959721 +/- 0.0021579979429949417</t>
+          <t>-0.020077344505317417 +/- 0.004488800274456184</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.013599742184982333 +/- 0.001263030482904651</t>
+          <t>-0.021205285207863335 +/- 0.002436488323742936</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.003416048984853315 +/- 0.0020944991052880223</t>
+          <t>0.007734450531743498 +/- 0.001389871650199668</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.0024492426683853765 +/- 0.0014135811923597374</t>
+          <t>0.01202062520141801 +/- 0.0013902452214065977</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.01659684176603282 +/- 0.0017128820194544812</t>
+          <t>0.011343860779890459 +/- 0.002771511440541433</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.022526587173702806 +/- 0.002149559284002878</t>
+          <t>0.03696422816629071 +/- 0.0034530914717988063</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.007669996777312227 +/- 0.0023095678849073863</t>
+          <t>0.010087012568482146 +/- 0.002508940525188786</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.0005156300354495103 +/- 0.0017004068267190405</t>
+          <t>-0.0024492426683853986 +/- 0.0013913653332209206</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.001224621334192666 +/- 0.001517061204761795</t>
+          <t>0.004640670319046114 +/- 0.002989292587896913</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>-0.00035449564937162226 +/- 0.0010536759732047562</t>
+          <t>0.002642603931679044 +/- 0.0014032575608815337</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0.0026426039316789773 +/- 0.0013883763602022478</t>
+          <t>0.00454398968739933 +/- 0.0014658801695835169</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.00025781501772473845 +/- 0.00040251356741206537</t>
+          <t>-0.00041894940380274857 +/- 0.000479086972198488</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.012600708991298703 +/- 0.002531195032659878</t>
+          <t>0.018788269416693537 +/- 0.0035713720059194327</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.0028359651949725452 +/- 0.0012630304829046287</t>
+          <t>0.002094747019013876 +/- 0.0021678414513492832</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.00512407347728 +/- 0.0014372609165953982</t>
+          <t>0.0007412181759587577 +/- 0.00167486773576362</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.0023525620367385925 +/- 0.0012975070666579218</t>
+          <t>-3.222687721556872e-05 +/- 0.0013782407206150852</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.004092813406380858 +/- 0.0014198124893271358</t>
+          <t>0.005575249758298461 +/- 0.002171670717219643</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.00032226877215593144 +/- 0.000407641335503489</t>
+          <t>0.000386722526587191 +/- 0.0008127309192986316</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0.0005478569126651344 +/- 0.0016561605101552807</t>
+          <t>-0.004382855301321287 +/- 0.0024971151308811478</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0.006574282951981925 +/- 0.0015535895318329299</t>
+          <t>0.006155333548179198 +/- 0.003045226748692624</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>-0.0037383177570093906 +/- 0.0021386606539525884</t>
+          <t>0.005704157267160825 +/- 0.001107498567672545</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.005575249758298362 +/- 0.0019868595090942226</t>
+          <t>9.668063164681717e-05 +/- 0.0022001777877793493</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>-0.0005478569126652122 +/- 0.0008653381619141261</t>
+          <t>0.00032226877215598695 +/- 0.0007060555043572839</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.00038672252658720205 +/- 0.0004950786817833482</t>
+          <t>0.0009668063164679386 +/- 0.0010785175978524966</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -5051,122 +5051,122 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.0002578150177247274 +/- 0.0013808756226637727</t>
+          <t>-3.222687721556872e-05 +/- 0.002130145390868318</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.002578150177247762 +/- 0.0015184297762667995</t>
+          <t>-0.0007734450531743153 +/- 0.0019346865639450503</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>-0.000741218175958791 +/- 0.0006453427133258541</t>
+          <t>0.0016757976152110942 +/- 0.0009753622913581466</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>0.00038672252658712437 +/- 0.00079985005774998</t>
+          <t>0.0009345794392523587 +/- 0.0009822591462538457</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.0011923944569771638 +/- 0.001611666097331615</t>
+          <t>0.0018369320012891154 +/- 0.001367650349592187</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>0.0031260070899129188 +/- 0.001188905365497687</t>
+          <t>-0.0027070576861101814 +/- 0.0012987071659432943</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>0.0006767644215274982 +/- 0.0005085315448939557</t>
+          <t>0.0014502094747019356 +/- 0.0008796225629362518</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.0026748308088945572 +/- 0.0013523773933842996</t>
+          <t>0.0021269738962294894 +/- 0.0017838675479340208</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.00206252014179823 +/- 0.0019076569238735005</t>
+          <t>0.0017402513696423093 +/- 0.0021043928736467266</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>-0.0014502094747019466 +/- 0.001924190169323645</t>
+          <t>-0.0008701256848211214 +/- 0.0018683252388831163</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-0.0020947470190139095 +/- 0.0014925602548384851</t>
+          <t>0.0008701256848211881 +/- 0.0028970152262931402</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.012052852078633536 +/- 0.0026347319930350856</t>
+          <t>0.0240090235256204 +/- 0.0025912092720238693</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.006799871092491083 +/- 0.0014729480995200191</t>
+          <t>0.0034160489848534038 +/- 0.0021240421596241095</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.0039961327747340845 +/- 0.0016508215887677386</t>
+          <t>0.000805671930389984 +/- 0.0025262665288128825</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>0.0007089912987431113 +/- 0.0007320539279149466</t>
+          <t>-0.0007089912987431113 +/- 0.0008502034133595129</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>0.0002578150177247274 +/- 0.0015101997439716328</t>
+          <t>0.0015791169835643216 +/- 0.001260149197294049</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>-0.005800837898807665 +/- 0.0018568946556091247</t>
+          <t>-0.00908797937479856 +/- 0.003449329851178768</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-0.015243312922977825 +/- 0.0013752232222592332</t>
+          <t>0.002320335159523068 +/- 0.00212208541838922</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-0.014308733483725489 +/- 0.0017663151280753653</t>
+          <t>-0.0036094102481469157 +/- 0.0018389097799145515</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-0.001385755720270776 +/- 0.0007495780438036125</t>
+          <t>3.222687721563533e-05 +/- 0.0006190580957878986</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>-0.0019013857557203195 +/- 0.001276526092190685</t>
+          <t>-0.0016757976152110498 +/- 0.000657301903137959</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>-0.0001289075088624303 +/- 0.0002578150177247773</t>
+          <t>0.0001289075088624081 +/- 0.00025781501772477455</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.001321301965839472 +/- 0.0016958198023748505</t>
+          <t>0.01160167579761524 +/- 0.0034075255914627995</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-0.016596841766032943 +/- 0.0016636686431376327</t>
+          <t>-0.009313567515307764 +/- 0.002105626325996739</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5176,147 +5176,147 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>-0.0014179825974863336 +/- 0.0008790320139855687</t>
+          <t>-0.0007089912987431335 +/- 0.0008502034133595111</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>0.004866258459555195 +/- 0.0011836524442286136</t>
+          <t>0.0030615533354818258 +/- 0.003095290478939498</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-0.011827263938124421 +/- 0.0013054868901404431</t>
+          <t>-0.004253947792458879 +/- 0.002001182687239454</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>-0.0006767644215275759 +/- 0.0009608798914518517</t>
+          <t>0.0017402513696423093 +/- 0.0013224804723611443</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-0.0024492426683854983 +/- 0.0010312600708991355</t>
+          <t>0.0014502094747019245 +/- 0.0016448340515855366</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-0.005478569126651689 +/- 0.0014412297631323193</t>
+          <t>-0.014308733483725411 +/- 0.0015535895318329299</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>0.003351595230422111 +/- 0.0021240421596241178</t>
+          <t>0.0034805027392845965 +/- 0.0018835500091785374</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-0.00038672252658721317 +/- 0.0011329936082015344</t>
+          <t>0.004769577827908489 +/- 0.001358124879516964</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>-0.00019336126329362325 +/- 0.0004371466312036943</t>
+          <t>0.00022558814050921416 +/- 0.0002516999573285966</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>-0.0004189494038028041 +/- 0.001857174287363708</t>
+          <t>-0.0025459233000321934 +/- 0.0013554457521632616</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>-0.0037705446342249926 +/- 0.0017297759459000452</t>
+          <t>-0.003190460844344145 +/- 0.0013007048708095804</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-0.0001289075088624303 +/- 0.0002578150177247773</t>
+          <t>-0.001353528843055074 +/- 0.0010957138253303276</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>0.0012246213341926548 +/- 0.0015101997439716458</t>
+          <t>-0.003319368353206553 +/- 0.0015525864609018164</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>0.004930712213986421 +/- 0.0010196127631038577</t>
+          <t>-0.0012246213341926882 +/- 0.0013958367919888952</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>0.0006445375443118962 +/- 0.0015388122960120218</t>
+          <t>-0.002223654527876218 +/- 0.0021543854222827114</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>-3.222687721562423e-05 +/- 0.00022558814050917925</t>
+          <t>-0.0002578150177247718 +/- 0.00045117628101835856</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>-0.0006445375443120072 +/- 0.00047800183610026344</t>
+          <t>-0.00016113438607796572 +/- 0.0007794641716047639</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>3.222687721554651e-05 +/- 0.0007270714903434395</t>
+          <t>-0.0016757976152110498 +/- 0.0004736364310892369</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
         <is>
+          <t>6.445375443120405e-05 +/- 0.0001289075088624081</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>-0.0005800837898807143 +/- 0.000688177779699086</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>0.00796003867225269 +/- 0.0017417427156779504</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>-0.00035449564937163337 +/- 0.00036602696395749573</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>-0.003061553335481848 +/- 0.0013842559842033228</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>-0.00019336126329361214 +/- 0.0004371466312037074</t>
+          <t>0.00022558814050922528 +/- 0.00045689483979237264</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>-0.0007734450531744153 +/- 0.001971905709413909</t>
+          <t>-0.006090879793747972 +/- 0.001209688970617049</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>0.0040283596519496865 +/- 0.0013691682749756985</t>
+          <t>0.007573316145665499 +/- 0.0016065025563151308</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>-0.000773445053174393 +/- 0.0010005913436197157</t>
+          <t>9.668063164682827e-05 +/- 0.0007633077204206843</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>0.004866258459555228 +/- 0.0014444688901717683</t>
+          <t>-0.0018047051240734468 +/- 0.001841167496885029</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>0.0012890750886238589 +/- 0.0019443252502737002</t>
+          <t>0.002610377054463453 +/- 0.0018482050865535967</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>0.0020625201417982077 +/- 0.0012987071659432768</t>
+          <t>0.00857234933934905 +/- 0.0007377069379477699</t>
         </is>
       </c>
     </row>
